--- a/prototype/output/employer_format/employee_to_bus_mapping_per_day.xlsx
+++ b/prototype/output/employer_format/employee_to_bus_mapping_per_day.xlsx
@@ -913,7 +913,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>11001526, 11015073, 11020130, 11026251, 11026494, 11026632, 11026889, 11027066, 11027077, 11027164, 11027324, 11027350, 11027562, 11027799, 11027865, 11027905, 11027932, 11028021, 11028333, 11028395, 11028556, 11028873, 11028959, 11029267, 11029277, 11029340, 11029585, 11029701, 11030075</t>
+          <t>11001526, 11015073, 11020130, 11026494, 11026632, 11026889, 11027066, 11027077, 11027090, 11027164, 11027324, 11027350, 11027562, 11027799, 11027865, 11027905, 11027932, 11028021, 11028333, 11028395, 11028556, 11028873, 11028959, 11029267, 11029277, 11029340, 11029585, 11029701, 11030075</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>23:09</t>
+          <t>00:23</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>11027058, 11027090, 11027292, 11027444, 11027533, 11027660, 11027858, 11027971, 11028023, 11028366, 11028574, 11028660, 11028865, 11029106, 11029413, 11029474, 11029784, 11029887, 11029917, 11029948</t>
+          <t>11017088, 11020174, 11026750, 11027000, 11027068, 11027070, 11027329, 11027533, 11027916, 11028234, 11028467, 11028574, 11028689, 11028691, 11028960, 11029393, 11029394, 11029413, 11029801, 11029858, 11029941</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>22:42</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>11017088, 11020174, 11026750, 11027000, 11027068, 11027070, 11027329, 11027916, 11028234, 11028467, 11028689, 11028691, 11028960, 11029268, 11029393, 11029394, 11029700, 11029801, 11029858, 11029941</t>
+          <t>11026251, 11027058, 11027292, 11027444, 11027660, 11027858, 11027971, 11028023, 11028366, 11028660, 11028865, 11029106, 11029268, 11029474, 11029700, 11029784, 11029887, 11029917, 11029948</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -2975,15 +2975,15 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>06:48</t>
+          <t>06:37</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>11024000, 11024389, 11026721, 11027703, 11027885, 11027939, 11027969, 11028080, 11028177, 11028334, 11028558, 11028690, 11028703, 11028904, 11028981, 11029223, 11029673, 11029794, 11029825, 11030155, 11030195</t>
+          <t>11024000, 11024389, 11026555, 11026721, 11027703, 11027885, 11027904, 11027939, 11027947, 11028080, 11028177, 11028348, 11028565, 11028589, 11028690, 11028703, 11028904, 11029223, 11029673, 11029794, 11029825, 11030155</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>06:17</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>11024033, 11024562, 11026756, 11026847, 11027101, 11027846, 11027889, 11027904, 11027947, 11028017, 11028020, 11028178, 11028402, 11028408, 11028589, 11029236, 11029272, 11029289, 11029976, 11029977, 11030118, 11030182</t>
+          <t>11024415, 11024745, 11026240, 11027204, 11027334, 11027462, 11027613, 11027690, 11028341, 11028344, 11028746, 11028747, 11029108, 11029191, 11029219, 11029403, 11029405, 11029797, 11029925, 11030001, 11030084, 11030224</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3279,15 +3279,15 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>04:13</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>11024415, 11026240, 11027204, 11027334, 11027400, 11027462, 11028341, 11028344, 11028611, 11028747, 11028849, 11029108, 11029164, 11029191, 11029219, 11029403, 11029405, 11029797, 11029925, 11030001, 11030084, 11030224</t>
+          <t>11026454, 11026673, 11027298, 11027711, 11027902, 11027969, 11028218, 11028334, 11028558, 11028599, 11028693, 11028953, 11028955, 11028981, 11029161, 11029286, 11029290, 11029292, 11029456, 11029951, 11030195</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -3312,20 +3312,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>06:23</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>11020116, 11021307, 11026745, 11026890, 11026934, 11026956, 11027066, 11027582, 11027717, 11027928, 11027946, 11027957, 11028021, 11028433, 11028556, 11028840, 11028905, 11029261, 11029267, 11029587, 11029701, 11030055, 11030175</t>
+          <t>11019663, 11024106, 11026706, 11026707, 11026726, 11026860, 11027370, 11027403, 11028575, 11028809, 11029195, 11029237, 11029252, 11029273, 11029338, 11029483, 11029856, 11029878, 11029910, 11029926, 11029938, 11029968</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3350,20 +3350,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>11024296, 11025033, 11026333, 11026884, 11027060, 11027164, 11027366, 11027525, 11027712, 11027713, 11027799, 11027856, 11028014, 11028217, 11028553, 11028959, 11029262, 11029276, 11029863, 11030111</t>
+          <t>11007975, 11020175, 11021740, 11026237, 11026244, 11026281, 11026615, 11026932, 11026945, 11027365, 11028340, 11028588, 11028859, 11028877, 11029353, 11029428, 11029498, 11029675, 11029765, 11029811, 11029912, 11029987</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3373,35 +3373,35 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>03:53</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>11026454, 11026555, 11026673, 11027298, 11027711, 11027902, 11028218, 11028348, 11028533, 11028565, 11028599, 11028693, 11028953, 11028955, 11029161, 11029286, 11029290, 11029292, 11029325, 11029456, 11029951</t>
+          <t>11004911, 11026568, 11026801, 11026812, 11026822, 11026831, 11026943, 11027375, 11027565, 11027849, 11028302, 11028946, 11028991, 11029117, 11029156, 11029334, 11029454, 11029561, 11029757, 11029903, 11030093, 11030211</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -3411,35 +3411,35 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>06:23</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>11019663, 11024106, 11026706, 11026707, 11026726, 11026860, 11027370, 11027403, 11028575, 11028809, 11029195, 11029237, 11029252, 11029273, 11029338, 11029483, 11029856, 11029878, 11029910, 11029926, 11029938, 11029968</t>
+          <t>11024296, 11025033, 11026333, 11026884, 11027060, 11027164, 11027366, 11027525, 11027712, 11027713, 11027799, 11027856, 11028014, 11028217, 11028553, 11028959, 11029262, 11029276, 11029863, 11030111</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3454,30 +3454,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>06:16</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>11007975, 11020175, 11021740, 11026237, 11026244, 11026281, 11026615, 11026932, 11026945, 11027365, 11028340, 11028588, 11028859, 11028877, 11029353, 11029428, 11029498, 11029675, 11029765, 11029811, 11029912, 11029987</t>
+          <t>11024033, 11024562, 11026756, 11026847, 11027101, 11027846, 11027889, 11028017, 11028020, 11028178, 11028402, 11028408, 11028533, 11029236, 11029272, 11029289, 11029325, 11029976, 11029977, 11030118, 11030182</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3492,30 +3492,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11004911, 11026568, 11026801, 11026812, 11026822, 11026831, 11026943, 11027375, 11027565, 11027849, 11028302, 11028946, 11028991, 11029117, 11029156, 11029334, 11029454, 11029561, 11029757, 11029903, 11030093, 11030211</t>
+          <t>11020116, 11021307, 11026745, 11026890, 11026934, 11026956, 11027066, 11027582, 11027717, 11027928, 11027946, 11027957, 11028021, 11028433, 11028556, 11028840, 11028905, 11029261, 11029267, 11029587, 11029701, 11030055, 11030175</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3568,12 +3568,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Trip 6</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3621,15 +3621,15 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>03:49</t>
+          <t>03:52</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>11024745, 11026648, 11027062, 11027390, 11027613, 11027685, 11027690, 11027717, 11027837, 11027847, 11027868, 11027875, 11028568, 11028571, 11028746, 11029177, 11029264, 11029365, 11029928, 11029943</t>
+          <t>11026648, 11026942, 11027062, 11027390, 11027399, 11027685, 11027717, 11027837, 11027847, 11027868, 11027875, 11028568, 11028571, 11028707, 11029148, 11029177, 11029264, 11029365, 11029928, 11029943, 11029969</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -3811,15 +3811,15 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>04:25</t>
+          <t>04:38</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>11007757, 11025099, 11026347, 11026370, 11026554, 11026633, 11026903, 11026942, 11027096, 11027371, 11027399, 11028206, 11028441, 11028707, 11028937, 11029148, 11029170, 11029635, 11029638, 11029877, 11029969, 11030183</t>
+          <t>11007757, 11025099, 11026347, 11026370, 11026554, 11026633, 11026903, 11027096, 11027371, 11027400, 11028206, 11028441, 11028611, 11028849, 11028937, 11029164, 11029170, 11029635, 11029638, 11029877, 11030183</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -7237,7 +7237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7376,12 +7376,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11024270, 11026244, 11026281, 11026932, 11027096, 11027193, 11027365, 11027668, 11027943, 11029020, 11029265, 11029299, 11029353, 11029476, 11029557, 11029719, 11029765, 11029766, 11029798, 11029804, 11029912, 11029970</t>
+          <t>11007975, 11020175, 11021740, 11025099, 11026237, 11026478, 11026814, 11026945, 11027301, 11027402, 11028340, 11028588, 11028855, 11028859, 11028877, 11029168, 11029428, 11029498, 11029811, 11029909, 11029987, 11030333</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>11021111, 11024409, 11024762, 11026572, 11026631, 11026648, 11026801, 11026890, 11027582, 11027706, 11027767, 11027842, 11027849, 11028585, 11028746, 11029325, 11029419, 11029552, 11029809, 11029903, 11029928</t>
+          <t>11004911, 11026348, 11026568, 11026812, 11026822, 11026943, 11027375, 11027565, 11028302, 11028946, 11028991, 11029058, 11029117, 11029156, 11029334, 11029561, 11029757, 11029763, 11030093, 11030154, 11030211</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -7490,20 +7490,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>11024409, 11024745, 11024762, 11026308, 11026849, 11027435, 11027767, 11027869, 11029137, 11029141, 11029147, 11029311, 11029419, 11029552, 11029591, 11029731, 11029732, 11030144</t>
+          <t>11028013</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -7513,35 +7513,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Trip 7</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>02:05</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>11026348, 11028244, 11028286, 11028340, 11029117, 11029903, 11029987, 11030093</t>
+          <t>11023181, 11023597, 11023831, 11026370, 11026471, 11026950, 11027127, 11027201, 11028301, 11028727, 11028808, 11028891, 11028925, 11029374, 11029454, 11029498, 11029584, 11029924, 11030042, 11030078, 11030082, 11030334</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -7556,30 +7556,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02:05</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>11023181, 11023597, 11023831, 11026370, 11026471, 11026950, 11027127, 11027201, 11028301, 11028727, 11028808, 11028891, 11028925, 11029374, 11029454, 11029498, 11029584, 11029924, 11030042, 11030078, 11030082, 11030334</t>
+          <t>11024033, 11024562, 11026847, 11026907, 11027846, 11027889, 11027904, 11027947, 11028017, 11028020, 11028178, 11028402, 11028408, 11028589, 11028904, 11028981, 11029272, 11029825, 11030118, 11030155, 11030182</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -7594,30 +7594,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>11024415, 11026240, 11027204, 11027334, 11027400, 11027462, 11027877, 11028341, 11028344, 11028605, 11028747, 11029108, 11029164, 11029191, 11029219, 11029295, 11029528, 11029675, 11029797, 11029925, 11030084, 11030289</t>
+          <t>11023831, 11024024, 11026332, 11026333, 11026371, 11026866, 11027200, 11028605, 11028738, 11028891, 11028925, 11029374, 11029387, 11029815, 11030163</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -7632,30 +7632,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11024992, 11026679, 11026902, 11027094, 11027323, 11027690, 11028971, 11028987, 11029222, 11029371, 11029620, 11029731</t>
+          <t>11026503, 11026751, 11026802, 11026950, 11027201, 11027775, 11028186, 11028291, 11028924, 11029146, 11029329, 11029402, 11029429, 11030039, 11030107</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -7670,30 +7670,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>22:48</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>11024389, 11026449, 11026461, 11026516, 11027067, 11027711, 11027847, 11027868, 11027888, 11027939, 11027951, 11027969, 11028022, 11028332, 11028558, 11028567, 11028580, 11028690, 11029264, 11029365, 11029673, 11029943, 11030111</t>
+          <t>11020116, 11021307, 11026396, 11026454, 11026698, 11026745, 11027101, 11027660, 11028013, 11028134, 11028840, 11028865, 11029113, 11029236, 11029325, 11029587, 11029867, 11030055, 11030175</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -7703,35 +7703,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>05:06</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>11020175, 11021740, 11026237, 11026281, 11026308, 11026478, 11026814, 11026945, 11027301, 11028588, 11028605, 11028859, 11028877, 11029020, 11029168, 11029265, 11029428, 11029476, 11029804, 11029811, 11030288, 11030333</t>
+          <t>11001526, 11024389, 11026632, 11026866, 11027067, 11027939, 11027946, 11027951, 11028022, 11028162, 11028332, 11028567, 11028580, 11028690, 11029285, 11029673, 11029815, 11030111, 11030163</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -7741,35 +7741,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Trip 6</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>11026642, 11027893, 11027968, 11028296, 11028926, 11029116, 11029165, 11029438, 11029573, 11029719, 11029765, 11029766, 11029970, 11030091, 11030334</t>
+          <t>11026449, 11026461, 11026492, 11026689, 11027668, 11027888, 11027915, 11027927, 11027938, 11027943, 11028016, 11028223, 11028442, 11028806, 11029222, 11029371, 11029703, 11029798, 11029856, 11029916, 11029936, 11029974</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -7784,30 +7784,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>05:06</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11001526, 11024389, 11026632, 11026866, 11027067, 11027939, 11027946, 11027951, 11028022, 11028162, 11028332, 11028567, 11028580, 11028690, 11029285, 11029673, 11029815, 11030111, 11030163</t>
+          <t>11024389, 11026449, 11026461, 11026516, 11027067, 11027711, 11027847, 11027868, 11027888, 11027939, 11027951, 11027969, 11028022, 11028332, 11028558, 11028567, 11028580, 11028690, 11029264, 11029365, 11029673, 11029943, 11030111</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -7822,30 +7822,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11025826, 11026689, 11027251, 11027343, 11027418, 11027927, 11027938, 11028016, 11028222, 11028555, 11028911, 11029070, 11029222, 11029371, 11029703, 11029814, 11029916, 11029920, 11029923, 11029936</t>
+          <t>11020175, 11021740, 11026237, 11026281, 11026308, 11026478, 11026814, 11026945, 11027301, 11028588, 11028605, 11028859, 11028877, 11029020, 11029168, 11029265, 11029428, 11029476, 11029804, 11029811, 11030288, 11030333</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -7860,30 +7860,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>01:25</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>11023831, 11024024, 11026332, 11026333, 11026371, 11026866, 11027200, 11028605, 11028738, 11028891, 11028925, 11029374, 11029387, 11029815, 11030163</t>
+          <t>11005920, 11021111, 11026494, 11026555, 11026721, 11027298, 11027345, 11027715, 11027905, 11027947, 11027969, 11028177, 11028348, 11028523, 11028565, 11028589, 11028689, 11028691, 11029277, 11029393, 11029935, 11030075</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -7893,35 +7893,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>03:07</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>11026503, 11026751, 11026802, 11026950, 11027201, 11027775, 11028186, 11028291, 11028924, 11029146, 11029329, 11029402, 11029429, 11030039, 11030107</t>
+          <t>11024409, 11024762, 11026679, 11026867, 11026982, 11027565, 11027767, 11027775, 11028186, 11028291, 11028946, 11029017, 11029146, 11029178, 11029334, 11029402, 11030107, 11030211</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -7931,35 +7931,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>11023626, 11026027, 11026472, 11026612, 11026671, 11026689, 11026848, 11027072, 11027251, 11027302, 11027717, 11027927, 11027938, 11027941, 11028016, 11028066, 11028338, 11028409, 11028709, 11029319, 11029324, 11029372, 11029974, 11030175</t>
+          <t>11017088, 11026207, 11026673, 11027068, 11027070, 11027090, 11027444, 11027904, 11027947, 11027977, 11028010, 11028099, 11028234, 11028366, 11028531, 11028552, 11028574, 11028660, 11029196, 11029413, 11029474, 11029864, 11029941</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -7969,35 +7969,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Trip 6</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>21:27</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>11015482, 11026368, 11026730, 11026870, 11027367, 11027573, 11027601, 11027672, 11027715, 11028220, 11028694, 11029205, 11029287, 11029724, 11029773, 11029887, 11029935, 11029946, 11029979</t>
+          <t>11024415, 11027334, 11027400, 11027663, 11027760, 11027877, 11028341, 11028344, 11028937, 11029164, 11029194, 11029219, 11029295, 11029403, 11029470, 11029528, 11029635, 11029925, 11030001, 11030084, 11030183, 11030289</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -8012,30 +8012,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>03:07</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>11024409, 11024762, 11026679, 11026867, 11026982, 11027565, 11027767, 11027775, 11028186, 11028291, 11028946, 11029017, 11029146, 11029178, 11029334, 11029402, 11030107, 11030211</t>
+          <t>11007757, 11024745, 11026472, 11026648, 11026671, 11027368, 11027613, 11027690, 11027714, 11027891, 11027957, 11028163, 11028244, 11028286, 11028433, 11028441, 11028611, 11028707, 11028849, 11029141, 11029147, 11029148, 11029177, 11029201, 11029261, 11029591, 11029758, 11029809, 11029969, 11030028, 11030154</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -8050,30 +8050,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>11024876, 11026572, 11026901, 11027835, 11027853, 11027857, 11028438, 11029304, 11029349, 11029774, 11029778, 11029799, 11029830</t>
+          <t>11022532, 11023626, 11026027, 11026541, 11026612, 11026689, 11027072, 11027251, 11027302, 11027717, 11027927, 11027938, 11027941, 11028016, 11028338, 11028409, 11028411, 11028709, 11029324, 11030175</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -8083,35 +8083,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>04:06</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>11024415, 11027334, 11027400, 11027663, 11027760, 11027877, 11028341, 11028344, 11028937, 11029164, 11029194, 11029219, 11029295, 11029403, 11029470, 11029528, 11029635, 11029925, 11030001, 11030084, 11030183, 11030289</t>
+          <t>11026633, 11026942, 11027062, 11027390, 11027399, 11027663, 11027685, 11027837, 11027875, 11028206, 11028568, 11028571, 11028707, 11028937, 11029148, 11029177, 11029405, 11029483, 11029635, 11029934, 11029969</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -8121,35 +8121,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>06:48</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>11007757, 11024745, 11026472, 11026648, 11026671, 11027368, 11027613, 11027690, 11027714, 11027891, 11027957, 11028163, 11028244, 11028286, 11028433, 11028441, 11028611, 11028707, 11028849, 11029141, 11029147, 11029148, 11029177, 11029201, 11029261, 11029591, 11029758, 11029809, 11029969, 11030028, 11030154</t>
+          <t>11007122, 11015073, 11020130, 11026368, 11026533, 11026889, 11027077, 11027350, 11027562, 11027566, 11027672, 11027865, 11027901, 11027940, 11028220, 11028395, 11028563, 11028694, 11029287, 11029585</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -8159,27 +8159,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>11022368, 11023831, 11024106, 11024992, 11026706, 11026812, 11026869, 11026943, 11026999, 11027204, 11027303, 11027334, 11027370, 11027403, 11028575, 11028740, 11029156, 11029498, 11029763, 11029793, 11029910, 11030152</t>
+          <t>11026244, 11026890, 11026901, 11026932, 11027193, 11027365, 11027582, 11027668, 11027835, 11027853, 11027857, 11027943, 11027957, 11028433, 11028438, 11028533, 11029261, 11029719, 11029765, 11029774, 11029798, 11029799</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -8197,35 +8197,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Trip 6</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>01:43</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>11026934, 11028474</t>
+          <t>11001713, 11007975, 11019006, 11021764, 11023181, 11023597, 11026407, 11026408, 11026429, 11026431, 11026468, 11027018, 11027127, 11027565, 11027960, 11028946, 11029017, 11029334, 11029655, 11029659, 11030042, 11030211</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -8240,30 +8240,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>11024033, 11024562, 11026847, 11026907, 11027846, 11027889, 11027904, 11027947, 11028017, 11028020, 11028178, 11028402, 11028408, 11028589, 11028904, 11028981, 11029272, 11029825, 11030118, 11030155, 11030182</t>
+          <t>11025826, 11026642, 11026942, 11027096, 11027343, 11027399, 11027418, 11027893, 11028222, 11028244, 11028286, 11028296, 11028555, 11028911, 11029017, 11029070, 11029116, 11029165, 11029315, 11029483, 11029597, 11029703, 11029707, 11029719, 11029765, 11029814, 11029856, 11029903, 11029916, 11029920, 11029923, 11029936, 11030091</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -8278,30 +8278,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>11026890, 11026901, 11027056, 11027345, 11027582, 11027835, 11027853, 11027857, 11027957, 11028433, 11028438, 11028533, 11029261, 11029774, 11029799, 11029935</t>
+          <t>11024876, 11026472, 11026671, 11027430, 11028310, 11028856, 11029113, 11029304, 11029349, 11029830, 11029927, 11029974, 11029984, 11030125</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -8311,35 +8311,35 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>03:56</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>11001713, 11007975, 11019006, 11021764, 11023181, 11023597, 11026407, 11026408, 11026429, 11026431, 11026468, 11027018, 11027127, 11027565, 11027960, 11028946, 11029017, 11029334, 11029655, 11029659, 11030042, 11030211</t>
+          <t>11024270, 11025099, 11026347, 11026648, 11026903, 11027371, 11027842, 11027847, 11027868, 11027948, 11028441, 11028585, 11028611, 11028849, 11029264, 11029365, 11029638, 11029877, 11029928, 11029943</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -8349,35 +8349,35 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>11007122, 11015073, 11020130, 11026889, 11027066, 11027077, 11027324, 11027566, 11027865, 11027901, 11027932, 11028021, 11028333, 11028395, 11028405, 11028556, 11028563, 11029223, 11029267, 11029340, 11029585, 11029701</t>
+          <t>11024876, 11026323, 11026541, 11026572, 11026848, 11026901, 11027835, 11027853, 11027857, 11028066, 11028438, 11029304, 11029319, 11029349, 11029774, 11029778, 11029799, 11029830, 11030125</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -8387,35 +8387,35 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>06:35</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>11021548, 11023181, 11023597, 11024116, 11024117, 11026637, 11027127, 11027396, 11027432, 11027895, 11027960, 11028587, 11028673, 11028866, 11028867, 11029312, 11029333, 11029527, 11029879, 11030042, 11030136, 11030224</t>
+          <t>11026870, 11027050, 11027430, 11027567, 11028856, 11029293, 11029927</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -8430,30 +8430,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>03:56</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>11024270, 11025099, 11026347, 11026648, 11026903, 11027371, 11027842, 11027847, 11027868, 11027948, 11028441, 11028585, 11028611, 11028849, 11029264, 11029365, 11029638, 11029877, 11029928, 11029943</t>
+          <t>11027096, 11027451, 11027928, 11028950, 11029912, 11030035</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -8468,30 +8468,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>05:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11024745, 11026449, 11026461, 11026802, 11027368, 11027613, 11027690, 11027714, 11027869, 11027888, 11027915, 11028223, 11028442, 11028746, 11028806, 11028971, 11029311, 11029770, 11029974</t>
+          <t>11001526, 11024024, 11024409, 11024762, 11026632, 11027345, 11027799, 11028959, 11029419, 11029552</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -8506,30 +8506,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>11024296, 11025033, 11026319, 11026453, 11026721, 11026766, 11026884, 11027060, 11027090, 11027712, 11027713, 11027856, 11028014, 11028177, 11028217, 11028553, 11029262, 11029276, 11029724, 11029863, 11030012</t>
+          <t>11026207, 11027058, 11027292, 11027327, 11027858, 11027971, 11028010, 11028023, 11028339, 11028366, 11028533, 11028660, 11029106, 11029474, 11029784, 11029917, 11029948</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -8539,35 +8539,35 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>03:52</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>11001526, 11024024, 11024409, 11024762, 11026632, 11027345, 11027799, 11028959, 11029419, 11029552</t>
+          <t>11026555, 11026673, 11027298, 11027711, 11027902, 11028218, 11028348, 11028405, 11028558, 11028565, 11028599, 11028693, 11028953, 11029161, 11029286, 11029290, 11029456, 11030195</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -8577,27 +8577,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>05:15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>23:18</t>
+          <t>06:14</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>11017088, 11020174, 11027068, 11027070, 11027904, 11027932, 11028099, 11028234, 11028467, 11028531, 11028533, 11028552, 11028574, 11028692, 11028873, 11029266, 11029340, 11029394, 11029413, 11029688, 11029801</t>
+          <t>11007757, 11021548, 11022368, 11024116, 11024117, 11026637, 11027396, 11027432, 11027891, 11027895, 11028587, 11028673, 11028866, 11028867, 11029312, 11029333, 11029758, 11029879, 11030028, 11030136, 11030224</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -8620,30 +8620,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>06:34</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>03:52</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>11026555, 11026673, 11027298, 11027711, 11027902, 11028218, 11028348, 11028405, 11028558, 11028565, 11028599, 11028693, 11028953, 11029161, 11029286, 11029290, 11029456, 11030195</t>
+          <t>11024296, 11025033, 11026319, 11026453, 11026721, 11026766, 11026884, 11027060, 11027090, 11027573, 11027712, 11027713, 11027856, 11028014, 11028177, 11028217, 11028553, 11029262, 11029276, 11029724, 11029863, 11030012</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -8658,30 +8658,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>11026323, 11026368, 11026533, 11026848, 11026870, 11027050, 11027430, 11027562, 11027567, 11027672, 11027940, 11028066, 11028220, 11028694, 11028856, 11029287, 11029293, 11029319, 11029927</t>
+          <t>11026251, 11026633, 11026730, 11026750, 11026756, 11026822, 11027062, 11027367, 11027685, 11027837, 11027875, 11027916, 11027977, 11028568, 11028571, 11028981, 11029108, 11029170, 11029405, 11029934, 11029941, 11029977, 11029984</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -8696,30 +8696,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 5</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>11007718, 11016423, 11019663, 11024106, 11026706, 11026707, 11026999, 11027370, 11027403, 11028575, 11028740, 11029194, 11029273, 11029338, 11029498, 11029720, 11029793, 11029910, 11029926, 11030152</t>
+          <t>11024409, 11024745, 11024762, 11026308, 11026849, 11027435, 11027767, 11027869, 11029137, 11029141, 11029147, 11029311, 11029419, 11029552, 11029591, 11029731, 11029732, 11030144</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -8734,30 +8734,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 6</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>11026251, 11026633, 11026730, 11026750, 11026756, 11026822, 11027062, 11027367, 11027685, 11027837, 11027875, 11027916, 11027977, 11028568, 11028571, 11028981, 11029108, 11029170, 11029405, 11029934, 11029941, 11029977, 11029984</t>
+          <t>11004911, 11026348, 11026568, 11026812, 11026943, 11027375, 11028302, 11028340, 11028991, 11029117, 11029156, 11029561, 11029757, 11029763, 11029987, 11030093</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -8767,27 +8767,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>03:15</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>11025826, 11026942, 11027096, 11027343, 11027399, 11027418, 11028222, 11028555, 11028911, 11029017, 11029070, 11029315, 11029483, 11029597, 11029703, 11029707, 11029814, 11029856, 11029916, 11029920, 11029923, 11029936</t>
+          <t>11024415, 11026240, 11027204, 11027334, 11027400, 11027462, 11027877, 11028341, 11028344, 11028605, 11028747, 11029108, 11029164, 11029191, 11029219, 11029295, 11029528, 11029675, 11029797, 11029925, 11030084, 11030289</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -8805,35 +8805,35 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Trip 6</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>00:25</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>11024992, 11027094, 11027176, 11027451, 11027460, 11028013, 11028950, 11029196, 11029315, 11030035</t>
+          <t>11027056, 11027345, 11029935</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -8848,22 +8848,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>04:21</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>11026633, 11026942, 11027062, 11027390, 11027399, 11027663, 11027685, 11027837, 11027875, 11028206, 11028568, 11028571, 11028707, 11028937, 11029148, 11029177, 11029405, 11029483, 11029635, 11029934, 11029969</t>
+          <t>11021111, 11024409, 11024762, 11026572, 11026631, 11026648, 11026801, 11026890, 11027582, 11027706, 11027767, 11027842, 11027849, 11028585, 11028746, 11029325, 11029419, 11029552, 11029809, 11029903, 11029928</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -8886,30 +8886,30 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>05:58</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>11007757, 11021548, 11022368, 11024116, 11024117, 11026637, 11027396, 11027432, 11027891, 11027895, 11028587, 11028673, 11028866, 11028867, 11029312, 11029333, 11029758, 11029879, 11030028, 11030136, 11030224</t>
+          <t>11001526, 11024296, 11025033, 11026319, 11026632, 11026766, 11026884, 11027060, 11027366, 11027525, 11027712, 11027713, 11027799, 11027856, 11028014, 11028217, 11028553, 11028959, 11029262, 11029276, 11029863, 11030012</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -8919,35 +8919,35 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>11017088, 11026207, 11026673, 11027068, 11027070, 11027090, 11027444, 11027904, 11027947, 11027977, 11028010, 11028099, 11028234, 11028366, 11028531, 11028552, 11028574, 11028660, 11029196, 11029413, 11029474, 11029864, 11029941</t>
+          <t>11020174, 11027058, 11027292, 11027327, 11027858, 11027971, 11028023, 11028339, 11028467, 11029106, 11029268, 11029394, 11029688, 11029700, 11029784, 11029801, 11029917, 11029948, 11030195</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -8957,17 +8957,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -8995,35 +8995,35 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:37</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>11001526, 11024296, 11025033, 11026319, 11026632, 11026766, 11026884, 11027060, 11027366, 11027525, 11027712, 11027713, 11027799, 11027856, 11028014, 11028217, 11028553, 11028959, 11029262, 11029276, 11029863, 11030012</t>
+          <t>11017088, 11020174, 11027068, 11027070, 11027932, 11028099, 11028234, 11028467, 11028552, 11028873, 11029268, 11029340, 11029394, 11029688, 11029700, 11029801, 11029887</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -9033,7 +9033,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9048,20 +9048,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>04:11</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>11020174, 11027058, 11027292, 11027327, 11027858, 11027971, 11028023, 11028339, 11028467, 11029106, 11029268, 11029394, 11029688, 11029700, 11029784, 11029801, 11029917, 11029948, 11030195</t>
+          <t>11028162, 11029285</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -9071,7 +9071,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>06:16</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>11004911, 11026348, 11026568, 11026812, 11026822, 11026943, 11027375, 11027565, 11028302, 11028946, 11028991, 11029058, 11029117, 11029156, 11029334, 11029561, 11029757, 11029763, 11030093, 11030154, 11030211</t>
+          <t>11024106, 11025826, 11026706, 11026999, 11027251, 11027343, 11027370, 11027403, 11028222, 11028555, 11028575, 11028740, 11029070, 11029194, 11029498, 11029793, 11029814, 11029910, 11029920, 11029923, 11030152</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -9109,7 +9109,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -9124,20 +9124,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>11026370, 11026462, 11026611, 11027345, 11027533, 11027562, 11027567, 11027915, 11027940, 11027948, 11028214, 11028223, 11028442, 11028599, 11028693, 11028953, 11028960, 11029161, 11029286, 11029290, 11029456, 11029877, 11030013</t>
+          <t>11007718, 11016423, 11024745, 11026802, 11026869, 11026963, 11026992, 11027303, 11027368, 11027613, 11027690, 11027714, 11027869, 11028284, 11028557, 11028746, 11028971, 11029311, 11029464, 11029720, 11029770, 11029818</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -9147,7 +9147,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9162,20 +9162,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>23:43</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>11005920, 11026494, 11026721, 11027056, 11027715, 11027905, 11027947, 11027969, 11028177, 11028523, 11028589, 11028689, 11028691, 11029277, 11029393, 11029946, 11030075</t>
+          <t>11026867, 11027955, 11028301, 11028474, 11028727, 11028808, 11028934, 11029017, 11029584, 11029912, 11029924, 11030063, 11030082</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -9190,30 +9190,30 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 5</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>04:11</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>11028162, 11029285</t>
+          <t>11026370, 11026462, 11026611, 11027345, 11027533, 11027562, 11027567, 11027915, 11027940, 11027948, 11028214, 11028223, 11028442, 11028599, 11028693, 11028953, 11028960, 11029161, 11029286, 11029290, 11029456, 11029877, 11030013</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -9228,30 +9228,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 6</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>11007122, 11015073, 11020130, 11023626, 11026541, 11026889, 11027072, 11027077, 11027101, 11027350, 11027566, 11027573, 11027865, 11027901, 11027941, 11028395, 11028563, 11028709, 11029236, 11029585, 11030125</t>
+          <t>11021548, 11023181, 11023597, 11024116, 11024117, 11026637, 11027127, 11027396, 11027432, 11027895, 11027960, 11028587, 11028673, 11028866, 11028867, 11029312, 11029333, 11029527, 11029879, 11030042, 11030136, 11030224</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -9266,30 +9266,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 7</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>11027451, 11027928, 11028950, 11030035</t>
+          <t>11027968, 11028926, 11029438, 11029573, 11029766, 11029970, 11030334</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -9299,35 +9299,35 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>06:27</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>11026207, 11027058, 11027292, 11027327, 11027858, 11027971, 11028010, 11028023, 11028339, 11028366, 11028660, 11029106, 11029268, 11029474, 11029700, 11029784, 11029887, 11029917, 11029948</t>
+          <t>11024000, 11026454, 11026756, 11026890, 11027000, 11027066, 11027582, 11027703, 11027885, 11028021, 11028334, 11028533, 11028556, 11028703, 11029267, 11029289, 11029325, 11029701, 11029858, 11029951, 11029976, 11029977</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -9342,30 +9342,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>06:27</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>11024000, 11026454, 11026756, 11026890, 11027000, 11027066, 11027582, 11027703, 11027885, 11028021, 11028334, 11028533, 11028556, 11028703, 11029267, 11029289, 11029325, 11029701, 11029858, 11029951, 11029976, 11029977</t>
+          <t>11001526, 11020116, 11021307, 11026396, 11026454, 11026632, 11026698, 11026745, 11026890, 11026934, 11027101, 11027164, 11027191, 11027582, 11027660, 11027799, 11027905, 11028134, 11028612, 11028865, 11028959, 11029236, 11029277, 11029867</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -9380,30 +9380,30 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>11001526, 11020116, 11021307, 11026396, 11026454, 11026632, 11026698, 11026745, 11026890, 11026934, 11027101, 11027164, 11027191, 11027582, 11027660, 11027799, 11027905, 11028134, 11028612, 11028865, 11028959, 11029236, 11029277, 11029867</t>
+          <t>11026244, 11026801, 11026849, 11026902, 11026932, 11027193, 11027365, 11027402, 11027435, 11027849, 11028855, 11028987, 11029137, 11029299, 11029353, 11029557, 11029620, 11029731, 11029732, 11029909</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -9418,30 +9418,30 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:27</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>11026244, 11026801, 11026849, 11026902, 11026932, 11027193, 11027365, 11027402, 11027435, 11027849, 11028855, 11028987, 11029137, 11029299, 11029353, 11029557, 11029620, 11029731, 11029732, 11029909</t>
+          <t>11007718, 11016423, 11019663, 11026707, 11026860, 11027565, 11028391, 11028809, 11028946, 11029195, 11029237, 11029252, 11029273, 11029334, 11029338, 11029675, 11029720, 11029878, 11029926, 11029938, 11029968, 11030211</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -9451,35 +9451,35 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>07:07</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>11021111, 11022532, 11024876, 11026541, 11026611, 11027430, 11028310, 11028411, 11028856, 11029113, 11029304, 11029349, 11029830, 11029927, 11029984, 11030125, 11030175</t>
+          <t>11019663, 11023626, 11026707, 11026726, 11026860, 11027072, 11027101, 11027418, 11027941, 11028391, 11028709, 11028809, 11028911, 11029236, 11029237, 11029252, 11029273, 11029338, 11029878, 11029926, 11029938, 11029968</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -9494,30 +9494,30 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>11026492, 11026726, 11026860, 11026869, 11026963, 11026992, 11027303, 11027668, 11027943, 11028284, 11028391, 11028557, 11028809, 11029237, 11029252, 11029464, 11029798, 11029818, 11029856, 11029878, 11029938, 11029968</t>
+          <t>11024270, 11024992, 11026281, 11026679, 11026902, 11027094, 11027323, 11027690, 11028971, 11028987, 11029020, 11029222, 11029265, 11029299, 11029353, 11029371, 11029476, 11029557, 11029620, 11029731, 11029766, 11029804, 11029970</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -9532,30 +9532,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>11007975, 11020175, 11021740, 11025099, 11026237, 11026478, 11026814, 11026945, 11027301, 11027402, 11028340, 11028588, 11028855, 11028859, 11028877, 11029168, 11029428, 11029498, 11029811, 11029909, 11029987, 11030333</t>
+          <t>11026555, 11027050, 11027298, 11027902, 11028218, 11028348, 11028565</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -9570,30 +9570,30 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>11026555, 11027050, 11027298, 11027902, 11028218, 11028348, 11028565</t>
+          <t>11026462, 11027444, 11027904, 11028531, 11028574, 11028692, 11029205, 11029266, 11029413, 11029773, 11029864, 11030195</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -9608,30 +9608,30 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 5</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>11026462, 11027444, 11029205, 11029773, 11029864, 11030195</t>
+          <t>11022368, 11024106, 11026706, 11026869, 11026963, 11026992, 11026999, 11027204, 11027303, 11027370, 11027403, 11028284, 11028557, 11028575, 11028740, 11029464, 11029498, 11029793, 11029818, 11029910, 11030152</t>
         </is>
       </c>
       <c r="H63" t="n">
@@ -9646,30 +9646,30 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 6</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>22:29</t>
+          <t>00:25</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>11020116, 11021307, 11026396, 11026454, 11026698, 11026745, 11027101, 11027660, 11028013, 11028134, 11028840, 11028865, 11029236, 11029587, 11029867, 11030055</t>
+          <t>11024992, 11027094, 11027176, 11027451, 11027460, 11028950, 11029196, 11029315, 11030035</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -9737,18 +9737,94 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>11004911, 11007718, 11016423, 11019663, 11026568, 11026707, 11026860, 11026963, 11026992, 11027375, 11027565, 11028284, 11028302, 11028391, 11028557, 11028809, 11028946, 11028991, 11029195, 11029237, 11029252, 11029273, 11029334, 11029338, 11029561, 11029675, 11029720, 11029757, 11029878, 11029926, 11029938, 11029968, 11030211</t>
+          <t>11007122, 11015073, 11020130, 11026889, 11027066, 11027077, 11027324, 11027566, 11027865, 11027901, 11027932, 11028021, 11028333, 11028395, 11028405, 11028556, 11028563, 11029223, 11029267, 11029340, 11029585, 11029701</t>
         </is>
       </c>
       <c r="H66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Trip 3</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>20</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>11015482, 11026368, 11026848, 11026870, 11026934, 11027056, 11027573, 11027601, 11027672, 11027715, 11028066, 11028220, 11028694, 11029287, 11029319, 11029372, 11029724, 11029887, 11029946, 11029979</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Trip 4</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>2</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>11024992, 11028474</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9907,15 +9983,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11022368, 11026478, 11026814, 11026860, 11026869, 11026992, 11027303, 11028391, 11028557, 11028809, 11029195, 11029237, 11029252, 11029464, 11029675, 11029818, 11029878, 11029938, 11029968</t>
+          <t>11007718, 11007975, 11016423, 11019663, 11024106, 11026706, 11026707, 11026999, 11027370, 11027403, 11028575, 11028740, 11029273, 11029338, 11029470, 11029483, 11029720, 11029793, 11029856, 11029910, 11029926, 11030152</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -9991,7 +10067,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11020175, 11021740, 11026237, 11026281, 11026308, 11026615, 11026812, 11026943, 11026945, 11027301, 11028588, 11028859, 11028877, 11029020, 11029168, 11029265, 11029428, 11029476, 11029498, 11029797, 11029804, 11029811</t>
+          <t>11020175, 11021740, 11026237, 11026281, 11026308, 11026478, 11026615, 11026814, 11026945, 11027301, 11028588, 11028859, 11028877, 11029020, 11029168, 11029265, 11029428, 11029476, 11029498, 11029797, 11029804, 11029811</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -10016,20 +10092,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>11021548, 11023181, 11023597, 11024116, 11024117, 11026471, 11026637, 11027127, 11027201, 11027396, 11027432, 11027895, 11028587, 11028673, 11028866, 11028867, 11029312, 11029333, 11029527, 11029879, 11030136, 11030224</t>
+          <t>11026831, 11027893, 11027968, 11028296, 11028926, 11029116, 11029165, 11029438, 11029719, 11029766, 11030334</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -10067,7 +10143,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>11023181, 11023597, 11026332, 11026371, 11026867, 11026950, 11027127, 11027960, 11028738, 11028891, 11028925, 11028934, 11029058, 11029219, 11029374, 11029387, 11029498, 11030042</t>
+          <t>11023181, 11023597, 11023831, 11026332, 11026371, 11026867, 11026950, 11027127, 11027960, 11028738, 11028891, 11028925, 11028934, 11029058, 11029374, 11029387, 11029498, 11030042</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -10105,7 +10181,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>11024415, 11026633, 11026963, 11027204, 11027400, 11027877, 11028284, 11028341, 11028344, 11029108, 11029164, 11029170, 11029194, 11029295, 11029403, 11029405, 11029528, 11029925, 11029934, 11030001, 11030084, 11030289</t>
+          <t>11024415, 11026633, 11027204, 11027334, 11027400, 11027877, 11028341, 11028344, 11029108, 11029164, 11029170, 11029194, 11029219, 11029295, 11029403, 11029405, 11029528, 11029925, 11029934, 11030001, 11030084, 11030289</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -10130,20 +10206,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>11025099, 11026890, 11026901, 11026902, 11027193, 11027582, 11027668, 11027835, 11027842, 11027853, 11027857, 11027943, 11028163, 11028214, 11028438, 11028585, 11028987, 11029774, 11029798, 11029799, 11030288</t>
+          <t>11023831, 11024024, 11026333, 11026371, 11026516, 11026855, 11026866, 11027003, 11027200, 11027960, 11029374, 11029387, 11029420, 11029797, 11029815, 11030078, 11030107, 11030111, 11030163</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -10168,20 +10244,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11023831, 11024024, 11026333, 11026371, 11026516, 11026855, 11026866, 11027003, 11027200, 11027960, 11029374, 11029387, 11029420, 11029797, 11029815, 11030078, 11030107, 11030111, 11030163</t>
+          <t>11026503, 11026751, 11026867, 11026982, 11027368, 11027775, 11028186, 11028291, 11028891, 11028924, 11028925, 11029017, 11029146, 11029329, 11029429, 11030039, 11030042</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -10206,20 +10282,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>11026503, 11026751, 11026867, 11026982, 11027368, 11027775, 11028186, 11028291, 11028891, 11028924, 11028925, 11029017, 11029146, 11029329, 11029429, 11030039, 11030042</t>
+          <t>11004911, 11026348, 11026568, 11026812, 11026822, 11026943, 11027375, 11028302, 11028340, 11028991, 11029117, 11029156, 11029561, 11029757, 11029763, 11030093</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -10244,20 +10320,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>11024106, 11024409, 11024762, 11024992, 11026633, 11026706, 11027370, 11027403, 11027767, 11028575, 11029222, 11029371, 11029419, 11029483, 11029552, 11029620, 11029856, 11029910, 11029916, 11029936, 11030154</t>
+          <t>11015482, 11022532, 11026323, 11026541, 11026730, 11026848, 11026870, 11027567, 11028310, 11028411, 11028856, 11029293, 11029304, 11029319, 11029349, 11029372, 11029778, 11029830, 11029927, 11029979, 11029984, 11030125</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -10267,35 +10343,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Trip 7</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>02:13</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>11015482, 11022532, 11026323, 11026541, 11026611, 11026730, 11026848, 11026870, 11027367, 11028411, 11029205, 11029293, 11029304, 11029319, 11029349, 11029372, 11029778, 11029830, 11029935, 11029946, 11029979, 11030125</t>
+          <t>11026333, 11026516, 11027066, 11027164, 11027191, 11027799, 11027902, 11027955, 11028021, 11028556, 11028612, 11028959, 11029267, 11029701, 11030063</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -10305,35 +10381,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Trip 8</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>T8</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>23:38</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11026503, 11026751, 11026855, 11027003, 11027200, 11027767, 11028924, 11029419, 11029552</t>
+          <t>11024033, 11024562, 11026673, 11026756, 11026847, 11026907, 11027711, 11027846, 11027889, 11028017, 11028020, 11028080, 11028402, 11028693, 11029272, 11029286, 11029456, 11029794, 11029825, 11029977, 11030118, 11030182</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -10348,30 +10424,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>02:13</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11026333, 11026516, 11027066, 11027164, 11027191, 11027345, 11027799, 11027955, 11028021, 11028556, 11028612, 11028959, 11029267, 11029701, 11030063</t>
+          <t>11024389, 11026370, 11026449, 11026461, 11026648, 11027067, 11027711, 11027799, 11027847, 11027868, 11027939, 11027951, 11028022, 11028332, 11028348, 11028567, 11028580, 11028690, 11029264, 11029365, 11029638, 11029673, 11029877, 11029943</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -10386,30 +10462,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>11024033, 11024562, 11026673, 11026756, 11026847, 11026907, 11027711, 11027846, 11027889, 11028017, 11028020, 11028080, 11028402, 11028693, 11029272, 11029286, 11029456, 11029794, 11029825, 11029977, 11030118, 11030182</t>
+          <t>11026244, 11026801, 11026849, 11026902, 11026932, 11027193, 11027365, 11027402, 11027435, 11027849, 11028855, 11028987, 11029137, 11029299, 11029353, 11029620, 11029731, 11029732, 11029909</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -10424,30 +10500,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>11004911, 11026347, 11026348, 11026568, 11026642, 11026812, 11026822, 11026831, 11026903, 11026943, 11027371, 11027375, 11028302, 11028991, 11029117, 11029156, 11029454, 11029757, 11029763, 11029809, 11030091, 11030093</t>
+          <t>11022368, 11024992, 11026308, 11026860, 11026999, 11027204, 11028391, 11028740, 11028809, 11029141, 11029147, 11029195, 11029237, 11029252, 11029402, 11029470, 11029591, 11029675, 11029793, 11029878, 11029938, 11029968, 11030152</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -10462,30 +10538,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>23:38</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>11024415, 11026240, 11026726, 11026950, 11027334, 11027462, 11028341, 11028344, 11028605, 11028738, 11028747, 11029108, 11029191, 11029194, 11029219, 11029295, 11029403, 11029405, 11029528, 11029925, 11030084</t>
+          <t>11026503, 11026751, 11026855, 11027003, 11027200, 11027767, 11028924, 11029419, 11029552</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -10495,35 +10571,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>22:18</t>
+          <t>03:07</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>11028013</t>
+          <t>11024409, 11024762, 11026679, 11027201, 11027565, 11027767, 11027775, 11028186, 11028291, 11028946, 11029017, 11029146, 11029329, 11029334, 11029402, 11029429, 11030039, 11030107, 11030211</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -10538,30 +10614,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>03:07</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>11024409, 11024762, 11026679, 11027201, 11027565, 11027767, 11027775, 11028186, 11028291, 11028946, 11029017, 11029146, 11029329, 11029334, 11029402, 11029429, 11030039, 11030107, 11030211</t>
+          <t>11024415, 11026240, 11026726, 11026950, 11027334, 11027462, 11028341, 11028344, 11028605, 11028738, 11028747, 11029108, 11029191, 11029194, 11029219, 11029295, 11029403, 11029405, 11029528, 11029925, 11030084</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -10576,30 +10652,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>11024389, 11026370, 11026449, 11026461, 11026648, 11027067, 11027711, 11027799, 11027847, 11027868, 11027939, 11027951, 11028022, 11028332, 11028567, 11028580, 11028690, 11029264, 11029365, 11029638, 11029673, 11029877, 11029943, 11029984</t>
+          <t>11024106, 11024409, 11024762, 11026492, 11026633, 11026706, 11027370, 11027403, 11027767, 11028575, 11029222, 11029371, 11029419, 11029483, 11029552, 11029620, 11029856, 11029910, 11029916, 11029936, 11030154</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -10614,30 +10690,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>11026244, 11026801, 11026849, 11026902, 11026932, 11027193, 11027365, 11027402, 11027435, 11027849, 11028855, 11028987, 11029137, 11029299, 11029353, 11029620, 11029731, 11029732, 11029909</t>
+          <t>11021548, 11023181, 11023597, 11024116, 11024117, 11026471, 11026637, 11027127, 11027201, 11027396, 11027432, 11027895, 11028587, 11028673, 11028866, 11028867, 11029312, 11029333, 11029527, 11029879, 11030136, 11030224</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -10647,35 +10723,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>05:05</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>11020116, 11021111, 11021307, 11024876, 11026454, 11026698, 11026745, 11026956, 11027345, 11028533, 11028905, 11029946</t>
+          <t>11020130, 11024000, 11026848, 11026889, 11027000, 11027066, 11027566, 11027703, 11027885, 11028021, 11028405, 11028556, 11028558, 11028703, 11028960, 11028981, 11029267, 11029701, 11029858, 11030155</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -10690,30 +10766,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>05:05</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>11020130, 11024000, 11026848, 11026889, 11027000, 11027066, 11027566, 11027703, 11027885, 11028021, 11028405, 11028556, 11028558, 11028703, 11028960, 11028981, 11029267, 11029701, 11029858, 11030155</t>
+          <t>11025826, 11027343, 11027418, 11028222, 11028555, 11028911, 11029070, 11029222, 11029371, 11029597, 11029703, 11029707, 11029814, 11029916, 11029920, 11029923, 11029936</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -10728,30 +10804,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>11007718, 11007975, 11016423, 11019663, 11024106, 11026706, 11026707, 11026999, 11027370, 11027403, 11028575, 11028740, 11029273, 11029338, 11029470, 11029483, 11029720, 11029793, 11029856, 11029910, 11029926, 11030152</t>
+          <t>11026207, 11026555, 11026673, 11026698, 11026750, 11027056, 11027090, 11027444, 11027916, 11027977, 11028099, 11028531, 11028552, 11028574, 11028960, 11029268, 11029413, 11029700, 11029773, 11029864, 11029941</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -10766,12 +10842,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -10804,12 +10880,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -10842,12 +10918,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -10895,15 +10971,15 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>03:53</t>
+          <t>03:42</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>11025099, 11026370, 11026449, 11027842, 11027847, 11027868, 11027948, 11028214, 11028585, 11028611, 11028849, 11028971, 11029264, 11029365, 11029877, 11029928, 11029943</t>
+          <t>11026890, 11027050, 11027345, 11027430, 11027567, 11027582, 11028218, 11028310, 11028599, 11028856, 11028953, 11029161, 11029289, 11029290, 11029304, 11029976</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -10928,12 +11004,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>05:15</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>06:08</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -10941,7 +11017,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>11007757, 11021548, 11024116, 11024117, 11026637, 11027396, 11027432, 11027891, 11027895, 11028587, 11028673, 11028866, 11028867, 11029312, 11029333, 11029527, 11029758, 11029879, 11030028, 11030136, 11030224</t>
+          <t>11026027, 11026631, 11026689, 11026802, 11027251, 11027302, 11027368, 11027668, 11027706, 11027714, 11027717, 11027869, 11027927, 11027938, 11027943, 11028016, 11028338, 11028746, 11029201, 11029311, 11029798</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -10966,20 +11042,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>11015482, 11024296, 11025033, 11026319, 11026766, 11026870, 11026884, 11027060, 11027366, 11027525, 11027567, 11027712, 11027713, 11027856, 11028014, 11028217, 11028553, 11029262, 11029276, 11029863, 11029979, 11030012</t>
+          <t>11007975, 11020175, 11021740, 11024270, 11026237, 11026281, 11026478, 11026615, 11026814, 11026945, 11027096, 11027301, 11028340, 11028588, 11028859, 11028877, 11029168, 11029222, 11029315, 11029371, 11029428, 11029498, 11029620, 11029811, 11029912</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -11017,7 +11093,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11001526, 11024024, 11024409, 11024762, 11026632, 11027164, 11027345, 11028959, 11029419, 11029552</t>
+          <t>11001526, 11024024, 11024409, 11024762, 11026462, 11026632, 11027164, 11028959, 11029419, 11029552</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -11080,20 +11156,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>03:15</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>03:42</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>11026555, 11026890, 11027298, 11027582, 11027902, 11028218, 11028310, 11028348, 11028565, 11028599, 11028953, 11029161, 11029289, 11029290, 11029325, 11029976</t>
+          <t>11024270, 11026347, 11026903, 11026942, 11027062, 11027371, 11027399, 11027663, 11027685, 11027760, 11027837, 11027875, 11028441, 11028568, 11028571, 11028707, 11028937, 11029148, 11029177, 11029635, 11029969, 11030183</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -11118,20 +11194,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>05:15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>06:33</t>
+          <t>06:47</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>11026027, 11026631, 11026689, 11026802, 11027251, 11027302, 11027368, 11027668, 11027706, 11027714, 11027717, 11027869, 11027927, 11027938, 11027943, 11028016, 11028338, 11028746, 11029201, 11029311, 11029798</t>
+          <t>11022368, 11026860, 11026869, 11026963, 11026992, 11027303, 11028284, 11028391, 11028557, 11028809, 11029195, 11029237, 11029252, 11029464, 11029675, 11029818, 11029878, 11029938, 11029968</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -11156,12 +11232,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:17</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -11169,7 +11245,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>11026244, 11026679, 11026932, 11027323, 11027365, 11027402, 11027613, 11027690, 11028366, 11028660, 11028855, 11029020, 11029265, 11029299, 11029353, 11029474, 11029476, 11029557, 11029804, 11029909, 11029928, 11030013</t>
+          <t>11015482, 11024296, 11025033, 11026319, 11026766, 11026870, 11026884, 11027060, 11027366, 11027525, 11027712, 11027713, 11027856, 11028014, 11028217, 11028553, 11029262, 11029276, 11029863, 11029946, 11029979, 11030012</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -11232,12 +11308,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>03:45</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -11245,7 +11321,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>11024270, 11026347, 11026903, 11026942, 11027062, 11027371, 11027399, 11027663, 11027685, 11027760, 11027837, 11027875, 11028441, 11028568, 11028571, 11028707, 11028937, 11029148, 11029177, 11029635, 11029969, 11030183</t>
+          <t>11017088, 11020174, 11027058, 11027068, 11027070, 11027292, 11027327, 11027329, 11027858, 11027971, 11028023, 11028234, 11028339, 11028467, 11029106, 11029394, 11029688, 11029784, 11029801, 11029917, 11029948</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -11270,20 +11346,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>11007122, 11023626, 11026612, 11026901, 11027072, 11027077, 11027562, 11027865, 11027940, 11027941, 11028395, 11028409, 11028694, 11028709, 11029223, 11029287, 11029324, 11029585, 11029774, 11029799</t>
+          <t>11023181, 11023597, 11026471, 11027127, 11027201, 11027565, 11027893, 11027928, 11027968, 11028296, 11028926, 11028946, 11029116, 11029165, 11029334, 11029402, 11029438, 11029561, 11029719, 11029766, 11030211, 11030334</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -11308,20 +11384,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>11027096, 11027176, 11027451, 11027928, 11028950, 11029315, 11029912, 11030035</t>
+          <t>11026554, 11027062, 11027390, 11027400, 11027663, 11027685, 11027760, 11027837, 11027875, 11027877, 11028206, 11028568, 11028571, 11028937, 11029164, 11029170, 11029177, 11029178, 11029635, 11029934, 11030289</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -11346,20 +11422,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>11026554, 11027062, 11027390, 11027400, 11027663, 11027685, 11027760, 11027837, 11027875, 11027877, 11028206, 11028568, 11028571, 11028937, 11029164, 11029170, 11029177, 11029178, 11029635, 11029934, 11030289</t>
+          <t>11017088, 11020174, 11027068, 11027070, 11027329, 11027932, 11027969, 11027977, 11028234, 11028333, 11028467, 11028552, 11029268, 11029340, 11029394, 11029413, 11029587, 11029688, 11029700, 11029801, 11029887, 11030195</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -11369,35 +11445,35 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>04:11</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>11017088, 11020174, 11027068, 11027070, 11027329, 11027932, 11027969, 11027977, 11028234, 11028333, 11028467, 11028552, 11029268, 11029340, 11029394, 11029413, 11029587, 11029688, 11029700, 11029801, 11029887, 11030195</t>
+          <t>11028162, 11029285</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -11412,30 +11488,30 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>03:45</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>11020174, 11026750, 11027058, 11027292, 11027327, 11027329, 11027858, 11027916, 11027971, 11028023, 11028339, 11028467, 11029106, 11029394, 11029688, 11029784, 11029801, 11029917, 11029941, 11029948</t>
+          <t>11007122, 11023626, 11026612, 11026901, 11027072, 11027077, 11027562, 11027865, 11027940, 11027941, 11028395, 11028409, 11028694, 11028709, 11029223, 11029287, 11029324, 11029585, 11029774, 11029799</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -11450,30 +11526,30 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>11023181, 11023597, 11026471, 11027127, 11027201, 11027565, 11027893, 11027968, 11028296, 11028926, 11028946, 11028971, 11029116, 11029165, 11029334, 11029402, 11029438, 11029561, 11029719, 11029766, 11030211, 11030334</t>
+          <t>11027176, 11027451, 11027928, 11028950, 11030035</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -11488,12 +11564,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -11511,7 +11587,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>11015073, 11020130, 11024000, 11026454, 11026889, 11027562, 11027703, 11027885, 11027904, 11027905, 11027940, 11027947, 11027969, 11028099, 11028310, 11028531, 11028558, 11028589, 11028693, 11028694, 11028703, 11028981, 11029277, 11029286, 11029325, 11029456, 11029951, 11030075, 11030155</t>
+          <t>11015073, 11020130, 11024000, 11026889, 11027533, 11027562, 11027703, 11027885, 11027904, 11027905, 11027940, 11027947, 11027969, 11028010, 11028099, 11028531, 11028533, 11028558, 11028589, 11028693, 11028694, 11028703, 11028981, 11029277, 11029286, 11029325, 11029456, 11030075, 11030155</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -11526,12 +11602,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 5</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -11574,20 +11650,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>04:11</t>
+          <t>05:23</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>11028162, 11029285</t>
+          <t>11025099, 11026370, 11026449, 11027842, 11027847, 11027868, 11027948, 11028214, 11028585, 11028611, 11028849, 11028971, 11029264, 11029365, 11029877, 11029928, 11029943</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -11612,20 +11688,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>11022532, 11026461, 11026472, 11026541, 11026572, 11026611, 11027835, 11027853, 11027857, 11027888, 11027915, 11028223, 11028411, 11028438, 11028442, 11028806, 11029113, 11029304, 11029349, 11029830, 11029974, 11030125</t>
+          <t>11020116, 11021111, 11021307, 11026396, 11026572, 11026745, 11026801, 11026956, 11027094, 11027323, 11027613, 11027660, 11027849, 11027957, 11028134, 11028433, 11028806, 11028865, 11028905, 11029261, 11029573, 11029867, 11029903</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -11650,20 +11726,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>07:09</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>11025826, 11027343, 11027418, 11028222, 11028555, 11028911, 11029070, 11029222, 11029371, 11029597, 11029703, 11029707, 11029814, 11029916, 11029920, 11029923, 11029936</t>
+          <t>11024409, 11024762, 11027767, 11029419, 11029552</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -11688,20 +11764,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>11020116, 11021307, 11026396, 11026745, 11026801, 11026802, 11026890, 11026956, 11027582, 11027660, 11027849, 11027928, 11027957, 11028134, 11028433, 11028806, 11028865, 11028905, 11029261, 11029573, 11029867, 11029903</t>
+          <t>11026251, 11026472, 11026671, 11026756, 11027050, 11027101, 11027298, 11027345, 11027430, 11027888, 11027915, 11027957, 11028163, 11028218, 11028223, 11028442, 11028565, 11028599, 11029161, 11029236, 11029290, 11029974, 11029977</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -11726,20 +11802,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>11026251, 11026462, 11026472, 11026671, 11026756, 11027101, 11027345, 11027567, 11027888, 11027915, 11027957, 11028163, 11028223, 11028442, 11028599, 11028856, 11029161, 11029236, 11029290, 11029927, 11029974, 11029977, 11029984</t>
+          <t>11024745, 11026027, 11026642, 11026849, 11027323, 11027435, 11029137, 11029311, 11029557, 11029731, 11029732, 11030091, 11030144, 11030175</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -11764,20 +11840,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>00:31</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>11022368, 11024992, 11026308, 11026860, 11026999, 11027204, 11028391, 11028740, 11028809, 11029141, 11029147, 11029195, 11029237, 11029252, 11029402, 11029470, 11029591, 11029675, 11029793, 11029878, 11029938, 11029968, 11030152</t>
+          <t>11024992, 11027094, 11027176, 11027451, 11027460, 11028013, 11028950, 11029196, 11030035</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -11840,20 +11916,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>11007975, 11020175, 11021740, 11024270, 11026237, 11026281, 11026478, 11026615, 11026814, 11026945, 11027301, 11028340, 11028588, 11028859, 11028877, 11029168, 11029222, 11029371, 11029428, 11029498, 11029620, 11029811</t>
+          <t>11005920, 11026730, 11027066, 11027367, 11027946, 11028021, 11028474, 11028523, 11028556, 11028689, 11028691, 11028840, 11029205, 11029267, 11029393, 11029587, 11029701, 11029935, 11030055, 11030075</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -11878,20 +11954,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>11027094</t>
+          <t>11026207, 11026698, 11027056, 11028533, 11029773</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -11916,20 +11992,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>23:52</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>11026207, 11026462, 11028010, 11029773, 11030013</t>
+          <t>11005920, 11026396, 11026454, 11026555, 11027660, 11028013, 11028134, 11028348, 11028523, 11028689, 11028691, 11028865, 11029205, 11029393, 11029867, 11029935, 11029951</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -11939,35 +12015,35 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>11024745, 11026027, 11026492, 11026642, 11026849, 11027323, 11027435, 11029137, 11029311, 11029731, 11029732, 11030091, 11030144, 11030175</t>
+          <t>11015073, 11026368, 11026730, 11026750, 11027090, 11027324, 11027367, 11027460, 11027573, 11027601, 11027672, 11027901, 11027916, 11028066, 11028220, 11028563, 11029319, 11029372, 11029724, 11029927, 11029941, 11029984</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -11977,35 +12053,35 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Trip 6</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>21:44</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>11029454</t>
+          <t>11026244, 11026611, 11026679, 11026802, 11026932, 11027365, 11027402, 11027533, 11027690, 11028010, 11028366, 11028660, 11028855, 11028971, 11029020, 11029265, 11029299, 11029353, 11029474, 11029476, 11029557, 11029804, 11029909, 11029928</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -12020,30 +12096,30 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>11005920, 11026555, 11027050, 11027066, 11027946, 11028021, 11028348, 11028474, 11028523, 11028556, 11028565, 11028689, 11028691, 11028692, 11028840, 11029266, 11029267, 11029393, 11029587, 11029701, 11030055, 11030075</t>
+          <t>11004911, 11026347, 11026348, 11026568, 11026642, 11026812, 11026822, 11026831, 11026890, 11026903, 11026943, 11027371, 11027375, 11027582, 11028302, 11028991, 11029117, 11029156, 11029454, 11029757, 11029763, 11029809, 11030091, 11030093</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -12058,30 +12134,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>11024409, 11024762, 11027767, 11029419, 11029552</t>
+          <t>11007757, 11025099, 11026370, 11026631, 11026942, 11027399, 11027706, 11027714, 11027869, 11027891, 11027948, 11028214, 11028244, 11028286, 11028441, 11028611, 11028707, 11028849, 11029141, 11029147, 11029148, 11029201, 11029591, 11029703, 11029758, 11029770, 11029809, 11029969, 11030028, 11030144, 11030288</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -12096,30 +12172,30 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 5</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>11026332, 11027955, 11028301, 11028727, 11028808, 11028934, 11029584, 11029924, 11030063, 11030082</t>
+          <t>11020116, 11021111, 11021307, 11026572, 11026745, 11026956, 11027298, 11027345, 11028840, 11028905, 11029325, 11029858, 11030055</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -12129,35 +12205,35 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>11007757, 11025099, 11026370, 11026631, 11026942, 11027399, 11027706, 11027714, 11027869, 11027891, 11027948, 11028214, 11028244, 11028286, 11028441, 11028611, 11028707, 11028849, 11029141, 11029147, 11029148, 11029201, 11029591, 11029703, 11029758, 11029770, 11029809, 11029969, 11030028, 11030144, 11030288</t>
+          <t>11022532, 11024876, 11026461, 11026472, 11026541, 11026572, 11026611, 11027835, 11027853, 11027857, 11027888, 11027915, 11028223, 11028411, 11028438, 11028442, 11028806, 11029349, 11029830, 11029974, 11030013, 11030125</t>
         </is>
       </c>
       <c r="H63" t="n">
@@ -12167,35 +12243,35 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>21:57</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>11026348, 11026831, 11028340, 11029561, 11029719</t>
+          <t>11007757, 11021548, 11024116, 11024117, 11026637, 11027396, 11027432, 11027891, 11027895, 11028587, 11028673, 11028866, 11028867, 11029312, 11029333, 11029527, 11029758, 11029879, 11030028, 11030136, 11030224</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -12210,30 +12286,30 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>11015073, 11026368, 11026750, 11027050, 11027090, 11027324, 11027430, 11027460, 11027573, 11027601, 11027672, 11027901, 11027916, 11028066, 11028220, 11028563, 11028856, 11029319, 11029372, 11029724, 11029927, 11029941</t>
+          <t>11025099, 11026890, 11026901, 11026902, 11027193, 11027582, 11027668, 11027835, 11027842, 11027853, 11027857, 11027943, 11028163, 11028214, 11028438, 11028585, 11028987, 11029774, 11029798, 11029799, 11030288</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -12248,30 +12324,30 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>11017088, 11026673, 11027056, 11027068, 11027070, 11027090, 11027345, 11027430, 11027444, 11027533, 11027977, 11028010, 11028099, 11028234, 11028531, 11028552, 11028574, 11028960, 11029196, 11029268, 11029413, 11029700, 11029864</t>
+          <t>11001526, 11026251, 11026454, 11026494, 11026632, 11026890, 11026934, 11027164, 11027191, 11027345, 11027582, 11027799, 11027902, 11027905, 11028612, 11028692, 11028959, 11029266, 11029277, 11029946, 11029951, 11030013</t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -12286,30 +12362,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 5</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>11001526, 11021111, 11024876, 11026207, 11026251, 11026494, 11026632, 11026698, 11026890, 11026934, 11027164, 11027191, 11027298, 11027582, 11027799, 11027902, 11027905, 11028218, 11028533, 11028612, 11028959, 11029277</t>
+          <t>11026332, 11027955, 11028301, 11028727, 11028808, 11028934, 11029584, 11029924, 11030063, 11030082</t>
         </is>
       </c>
       <c r="H67" t="n">
@@ -12324,12 +12400,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 6</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -12347,7 +12423,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>11007122, 11026572, 11026612, 11026648, 11027056, 11027066, 11027077, 11027350, 11027865, 11027932, 11028021, 11028333, 11028395, 11028409, 11028433, 11028556, 11028873, 11029113, 11029223, 11029261, 11029267, 11029324, 11029340, 11029585, 11029701</t>
+          <t>11007122, 11024876, 11026462, 11026612, 11026648, 11027066, 11027077, 11027350, 11027865, 11027932, 11028021, 11028333, 11028395, 11028409, 11028433, 11028556, 11028873, 11029113, 11029223, 11029261, 11029267, 11029324, 11029340, 11029585, 11029701</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -12362,30 +12438,30 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 7</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>00:25</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>11027094, 11027176, 11027451, 11027460, 11028950, 11029196, 11029299, 11030035</t>
+          <t>11029454</t>
         </is>
       </c>
       <c r="H69" t="n">
@@ -12403,7 +12479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12517,7 +12593,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>11020130, 11026756, 11026890, 11027101, 11027298, 11027345, 11027582, 11027947, 11028218, 11028310, 11028334, 11028405, 11028558, 11028589, 11028599, 11029161, 11029236, 11029289, 11029290, 11029325, 11029976, 11029977</t>
+          <t>11020130, 11026756, 11026890, 11027101, 11027345, 11027567, 11027582, 11027947, 11028218, 11028310, 11028334, 11028405, 11028558, 11028589, 11028599, 11029161, 11029236, 11029289, 11029290, 11029304, 11029976, 11029977</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -12555,7 +12631,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11007122, 11015073, 11026533, 11026750, 11026889, 11027077, 11027090, 11027324, 11027350, 11027566, 11027573, 11027601, 11027672, 11027865, 11027901, 11028220, 11028395, 11028563, 11029223, 11029585, 11029724</t>
+          <t>11015073, 11026533, 11026750, 11026889, 11027077, 11027090, 11027324, 11027350, 11027566, 11027573, 11027601, 11027672, 11027865, 11027901, 11028220, 11028333, 11028395, 11028563, 11029223, 11029585, 11029724</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -12661,15 +12737,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>22:53</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>11021548, 11022368, 11023181, 11023597, 11024116, 11024117, 11026471, 11026637, 11027127, 11027396, 11027432, 11028587, 11028673, 11028866, 11028867, 11029312, 11029333, 11029454, 11029527, 11029879, 11030136, 11030154, 11030224</t>
+          <t>11001526, 11026368, 11026462, 11026533, 11026632, 11026730, 11027367, 11027573, 11027601, 11027672, 11027715, 11027799, 11027946, 11028013, 11028220, 11028959, 11029287, 11029724, 11029887, 11029927, 11029984</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -12770,12 +12846,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -12783,7 +12859,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>11026244, 11026281, 11026902, 11026932, 11027094, 11027365, 11027402, 11027668, 11027943, 11028214, 11028855, 11028987, 11029017, 11029020, 11029265, 11029476, 11029557, 11029573, 11029798, 11029804, 11029909, 11030039</t>
+          <t>11017088, 11027056, 11027068, 11027070, 11027090, 11027444, 11027711, 11027904, 11027947, 11027977, 11028099, 11028234, 11028348, 11028531, 11028552, 11028960, 11029268, 11029413, 11029700, 11029773, 11029864, 11029941</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -12859,7 +12935,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>11026503, 11026751, 11026867, 11026950, 11027201, 11027714, 11027775, 11028186, 11028291, 11028738, 11028891, 11028924, 11028925, 11029146, 11029170, 11029178, 11029329, 11029429, 11030078</t>
+          <t>11026503, 11026751, 11026867, 11026950, 11027201, 11027714, 11027775, 11028186, 11028291, 11028738, 11028891, 11028924, 11028925, 11029146, 11029170, 11029329, 11029429, 11030039, 11030078</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -12897,7 +12973,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>11020116, 11021307, 11026396, 11026745, 11026956, 11027660, 11027715, 11028013, 11028134, 11028865, 11028905, 11029867, 11029946</t>
+          <t>11020116, 11021307, 11026396, 11026745, 11026956, 11027298, 11027660, 11027715, 11028013, 11028134, 11028865, 11028905, 11029867</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -13011,7 +13087,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11024389, 11026449, 11026461, 11026634, 11026648, 11027067, 11027435, 11027711, 11027847, 11027868, 11027939, 11027951, 11028022, 11028332, 11028567, 11028580, 11028690, 11029137, 11029264, 11029365, 11029673, 11029731, 11029943</t>
+          <t>11024389, 11026449, 11026461, 11026634, 11026648, 11027067, 11027435, 11027847, 11027868, 11027939, 11027951, 11028022, 11028332, 11028567, 11028580, 11028690, 11028693, 11029137, 11029264, 11029365, 11029673, 11029731, 11029943</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -13125,7 +13201,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>11015482, 11022532, 11026572, 11026870, 11027050, 11027430, 11027567, 11027835, 11027853, 11027857, 11028438, 11028856, 11029113, 11029293, 11029304, 11029349, 11029778, 11029830, 11029927, 11029979, 11030125</t>
+          <t>11015482, 11022532, 11024876, 11026541, 11026730, 11026870, 11027835, 11027853, 11027857, 11028438, 11028856, 11029113, 11029293, 11029349, 11029778, 11029830, 11029927, 11029946, 11029979, 11029984, 11030125</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -13239,7 +13315,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>11024000, 11026323, 11026555, 11026721, 11027066, 11027703, 11027885, 11028021, 11028080, 11028177, 11028348, 11028556, 11028565, 11028703, 11028904, 11028960, 11029267, 11029701, 11029794, 11029825, 11029858, 11029951</t>
+          <t>11007122, 11024000, 11026323, 11026721, 11026848, 11027050, 11027066, 11027430, 11027703, 11027885, 11028021, 11028080, 11028177, 11028556, 11028565, 11028703, 11028904, 11028960, 11029267, 11029701, 11029794, 11029825</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -13277,7 +13353,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>11026802, 11026890, 11026901, 11027368, 11027582, 11027690, 11027835, 11027842, 11027853, 11027857, 11028163, 11028438, 11028533, 11028585, 11028746, 11029774, 11029799, 11029928</t>
+          <t>11026611, 11026679, 11026802, 11026890, 11026901, 11027582, 11027613, 11027690, 11027835, 11027853, 11027857, 11027957, 11028163, 11028433, 11028438, 11029774, 11029799, 11029928</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -13353,7 +13429,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>11019663, 11026707, 11026869, 11026963, 11026992, 11026999, 11027204, 11028284, 11028557, 11028740, 11029058, 11029273, 11029299, 11029315, 11029338, 11029464, 11029470, 11029793, 11029818, 11029926, 11030001, 11030152</t>
+          <t>11019663, 11026707, 11026963, 11026992, 11026999, 11027204, 11027301, 11028284, 11028557, 11028740, 11029058, 11029273, 11029315, 11029338, 11029464, 11029470, 11029793, 11029818, 11029926, 11030001, 11030152</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -13363,35 +13439,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>23:08</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>11026503, 11026751, 11026855, 11027003, 11027200, 11028924, 11029419, 11029552</t>
+          <t>11024415, 11026240, 11026726, 11027204, 11027334, 11027462, 11028341, 11028344, 11028605, 11028738, 11028747, 11029108, 11029191, 11029194, 11029219, 11029295, 11029403, 11029405, 11029528, 11029925, 11030084</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -13406,30 +13482,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>11024415, 11026240, 11026726, 11027204, 11027334, 11027462, 11028341, 11028344, 11028605, 11028738, 11028747, 11029108, 11029191, 11029194, 11029219, 11029295, 11029403, 11029405, 11029528, 11029925, 11030084</t>
+          <t>11027176, 11027451, 11027533, 11027928, 11028010, 11028950, 11030035</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -13444,12 +13520,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -13482,12 +13558,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -13505,7 +13581,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>11021111, 11026308, 11026370, 11026472, 11026572, 11026671, 11026730, 11026849, 11027367, 11027706, 11027888, 11027915, 11027948, 11028214, 11028223, 11028441, 11028442, 11028971, 11029141, 11029147, 11029201, 11029205, 11029311, 11029638, 11029770, 11029877, 11029935, 11029974, 11030028, 11030175, 11030288</t>
+          <t>11021111, 11024876, 11026308, 11026370, 11026472, 11026555, 11026671, 11026849, 11027367, 11027706, 11027888, 11027915, 11027948, 11028214, 11028223, 11028441, 11028442, 11028971, 11029141, 11029147, 11029201, 11029205, 11029311, 11029638, 11029770, 11029877, 11029935, 11029974, 11030028, 11030175, 11030288</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -13520,12 +13596,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -13553,35 +13629,35 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>04:08</t>
+          <t>23:08</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>11024270, 11026347, 11026554, 11026903, 11027371, 11027400, 11027663, 11027760, 11027877, 11028206, 11028441, 11028611, 11028849, 11028937, 11029164, 11029170, 11029178, 11029635, 11029934, 11030289</t>
+          <t>11026503, 11026751, 11026855, 11027003, 11027200, 11028924, 11029419, 11029552</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -13596,30 +13672,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>05:58</t>
+          <t>04:08</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>11021548, 11022368, 11024116, 11024117, 11026637, 11027396, 11027432, 11027895, 11028587, 11028673, 11028866, 11028867, 11029312, 11029333, 11029527, 11029879, 11030136, 11030154, 11030224</t>
+          <t>11024270, 11026347, 11026554, 11026903, 11027371, 11027400, 11027663, 11027760, 11027877, 11028206, 11028441, 11028611, 11028849, 11028937, 11029164, 11029170, 11029178, 11029635, 11029934, 11030289</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -13634,30 +13710,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>05:58</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11024296, 11025033, 11026319, 11026453, 11026766, 11026884, 11027060, 11027366, 11027525, 11027562, 11027712, 11027713, 11027856, 11027940, 11028014, 11028553, 11028694, 11029262, 11029276, 11029287, 11029863, 11030012</t>
+          <t>11021548, 11022368, 11024116, 11024117, 11026637, 11027396, 11027432, 11027895, 11028587, 11028673, 11028866, 11028867, 11029312, 11029333, 11029527, 11029879, 11030136, 11030154, 11030224</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -13672,30 +13748,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>11026207, 11026454, 11027056, 11027345, 11027562, 11027904, 11027940, 11027947, 11027969, 11028010, 11028218, 11028310, 11028334, 11028558, 11028589, 11028599, 11028693, 11028981, 11029161, 11029286, 11029290, 11029293, 11029304, 11029325, 11029456, 11029773, 11029887, 11029951, 11029984</t>
+          <t>11024296, 11025033, 11026319, 11026453, 11026766, 11026884, 11027060, 11027366, 11027525, 11027562, 11027712, 11027713, 11027856, 11027940, 11028014, 11028553, 11028694, 11029262, 11029276, 11029287, 11029863, 11030012</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -13710,30 +13786,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>11005920, 11026454, 11026494, 11026671, 11026698, 11027345, 11027904, 11027905, 11027957, 11027969, 11028163, 11028523, 11028689, 11028691, 11028840, 11029266, 11029277, 11029393, 11029587, 11030055, 11030075</t>
+          <t>11026323, 11026454, 11026848, 11027056, 11027298, 11027345, 11027562, 11027916, 11027940, 11027969, 11028218, 11028310, 11028334, 11028533, 11028558, 11028565, 11028599, 11028692, 11028694, 11028981, 11029161, 11029286, 11029290, 11029325, 11029456, 11029773, 11029887, 11029941, 11029951</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -13743,35 +13819,35 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 5</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>03:52</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>11024745, 11027062, 11027390, 11027613, 11027685, 11027690, 11027837, 11027875, 11028244, 11028286, 11028568, 11028571, 11028707, 11028971, 11029148, 11029177, 11029928, 11029969</t>
+          <t>11005920, 11020130, 11026207, 11026494, 11026671, 11026698, 11027000, 11027345, 11027905, 11027957, 11027969, 11028163, 11028523, 11028589, 11028689, 11028691, 11028840, 11029277, 11029393, 11030055, 11030075</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -13786,30 +13862,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>07:19</t>
+          <t>03:52</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>11024106, 11025826, 11026492, 11026633, 11026706, 11027343, 11027370, 11027403, 11027418, 11028222, 11028555, 11028575, 11028911, 11029070, 11029483, 11029597, 11029707, 11029814, 11029856, 11029910, 11029920, 11029923</t>
+          <t>11024745, 11027062, 11027390, 11027613, 11027685, 11027690, 11027837, 11027875, 11028244, 11028286, 11028568, 11028571, 11028707, 11028971, 11029148, 11029177, 11029928, 11029969</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -13824,30 +13900,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>11024296, 11025033, 11026319, 11026453, 11026462, 11026766, 11026884, 11027060, 11027366, 11027525, 11027712, 11027713, 11027856, 11028014, 11028217, 11028553, 11029262, 11029276, 11029863, 11030012</t>
+          <t>11024106, 11025826, 11026492, 11026633, 11026706, 11027343, 11027370, 11027403, 11027418, 11028222, 11028555, 11028575, 11028911, 11029070, 11029483, 11029597, 11029707, 11029814, 11029856, 11029910, 11029920, 11029923</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -13857,35 +13933,35 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>11024033, 11024562, 11026673, 11026847, 11026907, 11027711, 11027846, 11027889, 11028017, 11028020, 11028178, 11028402, 11028408, 11028693, 11028981, 11029272, 11029286, 11029456, 11030118, 11030155, 11030182</t>
+          <t>11020116, 11021111, 11021307, 11026745, 11026890, 11026956, 11027368, 11027390, 11027582, 11027842, 11027928, 11028585, 11028746, 11028806, 11028905, 11029113, 11029261</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -13895,35 +13971,35 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>21:27</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>11020116, 11021111, 11021307, 11024876, 11026207, 11026396, 11026679, 11026698, 11026745, 11026890, 11026956, 11027390, 11027582, 11027613, 11027660, 11027928, 11027957, 11028134, 11028433, 11028806, 11028865, 11028905, 11029261, 11029867</t>
+          <t>11015073, 11024296, 11025033, 11026319, 11026453, 11026766, 11026884, 11027060, 11027324, 11027366, 11027525, 11027712, 11027713, 11027856, 11028014, 11028217, 11028405, 11028553, 11029262, 11029276, 11029863, 11030012</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -13938,30 +14014,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>11024000, 11026027, 11026631, 11026756, 11026942, 11027000, 11027062, 11027101, 11027251, 11027399, 11027685, 11027703, 11027837, 11027869, 11027875, 11027885, 11028568, 11028571, 11028703, 11028856, 11029116, 11029177, 11029236, 11029703, 11029858, 11029927, 11029977, 11029984, 11030155</t>
+          <t>11024033, 11024562, 11026673, 11026847, 11026907, 11027711, 11027846, 11027889, 11028017, 11028020, 11028178, 11028402, 11028408, 11028693, 11028981, 11029272, 11029286, 11029456, 11030118, 11030155, 11030182</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -13976,30 +14052,30 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>21:56</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>11026642, 11026812, 11026831, 11026943, 11027968, 11028926, 11029156, 11029299, 11029438, 11029557, 11029763, 11029970, 11030091, 11030334</t>
+          <t>11026244, 11026281, 11026902, 11026932, 11027094, 11027365, 11027402, 11027668, 11027943, 11028214, 11028855, 11028987, 11029017, 11029020, 11029265, 11029353, 11029476, 11029557, 11029573, 11029798, 11029804, 11029909</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -14009,35 +14085,35 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>03:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>11020174, 11027058, 11027292, 11027327, 11027329, 11027533, 11027858, 11027971, 11028010, 11028023, 11028339, 11028366, 11028660, 11029106, 11029394, 11029474, 11029688, 11029784, 11029801, 11029917, 11029948</t>
+          <t>11024000, 11026027, 11026631, 11026756, 11026942, 11027000, 11027050, 11027062, 11027101, 11027251, 11027399, 11027430, 11027685, 11027703, 11027837, 11027869, 11027875, 11027885, 11028568, 11028571, 11028703, 11028856, 11029116, 11029177, 11029236, 11029703, 11029858, 11029977, 11030155</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -14047,35 +14123,35 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>21:56</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>11001526, 11026251, 11026494, 11026632, 11026934, 11027050, 11027164, 11027191, 11027298, 11027345, 11027430, 11027799, 11027902, 11027905, 11028348, 11028565, 11028612, 11028959, 11029277</t>
+          <t>11026642, 11026812, 11026831, 11026943, 11027968, 11028926, 11029156, 11029299, 11029438, 11029557, 11029763, 11029970, 11030091, 11030334</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -14090,30 +14166,30 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>03:45</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>11017088, 11026251, 11027068, 11027070, 11027444, 11027916, 11027932, 11027977, 11028099, 11028234, 11028333, 11028531, 11028552, 11028692, 11028873, 11029268, 11029340, 11029413, 11029700, 11029864, 11029941</t>
+          <t>11020174, 11027058, 11027292, 11027327, 11027329, 11027533, 11027858, 11027971, 11028010, 11028023, 11028339, 11028366, 11028660, 11029106, 11029394, 11029474, 11029688, 11029784, 11029801, 11029917, 11029948</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -14128,30 +14204,30 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>11022532, 11023626, 11024876, 11026323, 11026541, 11026611, 11026612, 11026648, 11026848, 11027072, 11027941, 11028066, 11028409, 11028411, 11028433, 11028709, 11029113, 11029261, 11029324, 11029372, 11029778, 11029830, 11030013, 11030125</t>
+          <t>11023181, 11023597, 11026471, 11026812, 11026943, 11027127, 11027893, 11027968, 11028244, 11028286, 11028296, 11028707, 11028926, 11029116, 11029156, 11029165, 11029438, 11029454, 11029763, 11029765, 11029970, 11030334</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -14166,30 +14242,30 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>00:38</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>11027176, 11027451, 11027460, 11028013, 11028950, 11029196, 11029353, 11030035</t>
+          <t>11017088, 11026251, 11027068, 11027070, 11027444, 11027904, 11027932, 11027947, 11027977, 11028099, 11028234, 11028531, 11028552, 11028873, 11029266, 11029268, 11029340, 11029413, 11029587, 11029700, 11029864</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -14199,35 +14275,35 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>04:11</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>11028162, 11029285</t>
+          <t>11021548, 11022368, 11023181, 11023597, 11024116, 11024117, 11026471, 11026637, 11026869, 11027127, 11027396, 11027432, 11028587, 11028673, 11028866, 11028867, 11029312, 11029333, 11029527, 11029879, 11030136, 11030154, 11030224</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -14242,30 +14318,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>06:09</t>
+          <t>04:11</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>11026027, 11026689, 11026848, 11026942, 11027251, 11027302, 11027399, 11027460, 11027668, 11027717, 11027927, 11027938, 11027943, 11028016, 11028338, 11028806, 11029319, 11029372, 11029703, 11029798, 11029916, 11029936</t>
+          <t>11028162, 11029285</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -14280,22 +14356,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>06:09</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -14303,7 +14379,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>11026461, 11026472, 11026541, 11026611, 11026631, 11026802, 11026901, 11027368, 11027706, 11027714, 11027869, 11027888, 11027915, 11028223, 11028411, 11028442, 11029201, 11029311, 11029770, 11029774, 11029799, 11029974</t>
+          <t>11026027, 11026689, 11026942, 11027251, 11027302, 11027399, 11027460, 11027668, 11027717, 11027927, 11027938, 11027943, 11028016, 11028338, 11028806, 11029196, 11029319, 11029372, 11029703, 11029798, 11029916, 11029936</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -14318,30 +14394,30 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>11027176, 11027451, 11027533, 11027928, 11028950, 11029196, 11030035</t>
+          <t>11026461, 11026472, 11026611, 11026631, 11026802, 11026901, 11027368, 11027706, 11027714, 11027869, 11027888, 11027915, 11028223, 11028411, 11028442, 11028533, 11029201, 11029311, 11029770, 11029774, 11029799, 11029974</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -14356,30 +14432,30 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>11026492, 11026554, 11026633, 11027334, 11027400, 11027663, 11027760, 11027877, 11028206, 11028937, 11029108, 11029164, 11029191, 11029219, 11029483, 11029528, 11029635, 11029766, 11030183, 11030289</t>
+          <t>11001526, 11026207, 11026251, 11026396, 11026494, 11026632, 11026698, 11026890, 11026934, 11027164, 11027191, 11027345, 11027582, 11027660, 11027799, 11027902, 11027905, 11028134, 11028612, 11028865, 11028959, 11029277, 11029867, 11029946</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -14394,30 +14470,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Trip 6</t>
+          <t>Trip 5</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>11001526, 11007122, 11015073, 11026632, 11027066, 11027077, 11027324, 11027350, 11027799, 11027865, 11027932, 11028021, 11028333, 11028395, 11028556, 11028873, 11028959, 11029223, 11029267, 11029340, 11029585, 11029701</t>
+          <t>11026492, 11026554, 11027334, 11027400, 11027663, 11027760, 11027877, 11028206, 11028937, 11029108, 11029164, 11029178, 11029191, 11029219, 11029483, 11029528, 11029635, 11029766, 11030183, 11030289</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -14432,30 +14508,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Trip 7</t>
+          <t>Trip 6</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>21:44</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>11020130, 11026368, 11026533, 11026730, 11026889, 11026934, 11027367, 11027566, 11027573, 11027601, 11027672, 11027715, 11027901, 11028220, 11028405, 11028563, 11028694, 11029205, 11029287, 11029724, 11029887, 11029935</t>
+          <t>11007122, 11020130, 11026889, 11027066, 11027077, 11027350, 11027566, 11027865, 11027901, 11027932, 11028021, 11028333, 11028395, 11028556, 11028563, 11028873, 11029223, 11029267, 11029340, 11029585, 11029701</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -14465,35 +14541,35 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 7</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>04:39</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>11026449, 11027842, 11027847, 11027868, 11028585, 11029264, 11029365, 11029638, 11029877, 11029943, 11030288, 11030333</t>
+          <t>11026648, 11026934, 11028433, 11029261</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -14508,30 +14584,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>04:39</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>11007718, 11007757, 11016423, 11019663, 11026707, 11026860, 11027891, 11028391, 11028809, 11029195, 11029237, 11029252, 11029273, 11029338, 11029675, 11029720, 11029758, 11029878, 11029926, 11029938, 11029968, 11030028</t>
+          <t>11026449, 11027842, 11027847, 11027868, 11028585, 11029264, 11029365, 11029638, 11029877, 11029943, 11030288, 11030333</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -14546,22 +14622,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -14569,7 +14645,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>11017088, 11026555, 11026673, 11027056, 11027068, 11027070, 11027090, 11027444, 11027977, 11028099, 11028234, 11028531, 11028552, 11028692, 11028960, 11029266, 11029268, 11029413, 11029700, 11029773, 11029864, 11029941</t>
+          <t>11007718, 11007757, 11016423, 11019663, 11026707, 11026860, 11027891, 11028391, 11028809, 11029195, 11029237, 11029252, 11029273, 11029338, 11029675, 11029720, 11029758, 11029878, 11029926, 11029938, 11029968, 11030028</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -14584,30 +14660,30 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>11024409, 11024762, 11029419, 11029552, 11030288, 11030333</t>
+          <t>11007975, 11020175, 11021740, 11024270, 11026237, 11026478, 11026615, 11026801, 11026814, 11026945, 11027301, 11027849, 11028340, 11028588, 11028859, 11028877, 11029168, 11029299, 11029428, 11029811, 11029903</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -14622,30 +14698,30 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>11007975, 11026237, 11026281, 11026308, 11026478, 11026814, 11026902, 11026945, 11027301, 11028588, 11028859, 11028877, 11028987, 11029020, 11029168, 11029265, 11029428, 11029476, 11029804, 11029811</t>
+          <t>11024409, 11024762, 11029419, 11029552, 11030288, 11030333</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -14660,30 +14736,30 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Trip 6</t>
+          <t>Trip 5</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>11025826, 11026689, 11027251, 11027302, 11027343, 11027418, 11027717, 11027927, 11027938, 11028016, 11028222, 11028338, 11028555, 11028911, 11029070, 11029597, 11029707, 11029814, 11029920, 11029923, 11030175</t>
+          <t>11026332, 11026982, 11027955, 11028301, 11028727, 11028808, 11028934, 11029584, 11029912, 11029924, 11030063, 11030082</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -14693,35 +14769,35 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 6</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>06:19</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>11001713, 11019006, 11021764, 11026408, 11026429, 11026431, 11026468, 11026515, 11027018, 11029289, 11029503, 11029655, 11029976</t>
+          <t>11007975, 11026237, 11026281, 11026308, 11026478, 11026814, 11026902, 11026945, 11027301, 11028588, 11028859, 11028877, 11028987, 11029020, 11029168, 11029265, 11029428, 11029476, 11029804, 11029811</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -14731,35 +14807,35 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 7</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>06:49</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>11007975, 11020175, 11021740, 11024270, 11026237, 11026478, 11026615, 11026801, 11026814, 11026945, 11027301, 11027849, 11028340, 11028588, 11028859, 11028877, 11029168, 11029353, 11029428, 11029811, 11029903</t>
+          <t>11025826, 11026689, 11027251, 11027302, 11027343, 11027418, 11027717, 11027927, 11027938, 11028016, 11028222, 11028338, 11028555, 11028911, 11029070, 11029597, 11029707, 11029814, 11029920, 11029923, 11030175</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -14769,35 +14845,35 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 8</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T8</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>11023181, 11023597, 11026471, 11026812, 11026943, 11027127, 11027893, 11027968, 11028244, 11028286, 11028296, 11028707, 11028926, 11029116, 11029156, 11029165, 11029438, 11029454, 11029763, 11029765, 11029970, 11030334</t>
+          <t>11027176, 11027451, 11027460, 11028950, 11029196, 11029299, 11030035</t>
         </is>
       </c>
       <c r="H63" t="n">
@@ -14812,30 +14888,30 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>06:19</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>11026332, 11026982, 11027955, 11028301, 11028727, 11028808, 11028934, 11029584, 11029912, 11029924, 11030063, 11030082</t>
+          <t>11001713, 11019006, 11021764, 11026408, 11026429, 11026431, 11026468, 11026515, 11027018, 11029289, 11029503, 11029655, 11029976</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -14850,30 +14926,30 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>06:49</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>11026244, 11026849, 11026932, 11027193, 11027365, 11027402, 11028244, 11028286, 11028855, 11029353, 11029732, 11029903, 11029909</t>
+          <t>11005920, 11026555, 11026673, 11027066, 11027367, 11028021, 11028474, 11028523, 11028556, 11028689, 11028691, 11028692, 11028840, 11029205, 11029266, 11029267, 11029393, 11029587, 11029701, 11029935, 11030055, 11030075</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -14888,30 +14964,30 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Trip 6</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>11024270, 11026347, 11026679, 11026903, 11027096, 11027323, 11027435, 11027690, 11028746, 11029137, 11029148, 11029222, 11029315, 11029591, 11029731, 11029732, 11029856, 11029916, 11029936, 11029969, 11030144</t>
+          <t>11026244, 11026849, 11026932, 11027193, 11027365, 11027402, 11028244, 11028286, 11028855, 11029353, 11029732, 11029903, 11029909</t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -14926,33 +15002,71 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Trip 7</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>T7</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>21</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>11024270, 11026347, 11026633, 11026679, 11026903, 11027096, 11027323, 11027435, 11027690, 11028746, 11029137, 11029148, 11029222, 11029591, 11029731, 11029732, 11029856, 11029916, 11029936, 11029969, 11030144</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Trip 5</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>21:21</t>
         </is>
       </c>
-      <c r="F67" t="n">
+      <c r="F68" t="n">
         <v>8</v>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>11015482, 11024409, 11024762, 11026870, 11029419, 11029552, 11029946, 11029979</t>
-        </is>
-      </c>
-      <c r="H67" t="n">
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>11015482, 11024409, 11024762, 11026870, 11029293, 11029419, 11029552, 11029979</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14967,7 +15081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15106,20 +15220,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11026281, 11026801, 11026902, 11027402, 11028855, 11028987, 11029017, 11029020, 11029265, 11029371, 11029476, 11029557, 11029620, 11029804, 11029909, 11029970, 11030039, 11030333</t>
+          <t>11007975, 11020175, 11021740, 11026237, 11026244, 11026478, 11026615, 11026814, 11026932, 11026945, 11027365, 11027371, 11028588, 11028859, 11028877, 11029168, 11029428, 11029454, 11029498, 11029765, 11029811</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -15187,7 +15301,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -15220,20 +15334,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>11007718, 11016423, 11019663, 11026707, 11026860, 11027565, 11028391, 11028809, 11028946, 11029058, 11029195, 11029237, 11029252, 11029273, 11029334, 11029338, 11029402, 11029675, 11029878, 11029926, 11029938, 11029968, 11030211</t>
+          <t>11007757, 11026631, 11026648, 11026802, 11026831, 11026903, 11026942, 11027368, 11027371, 11027399, 11027706, 11027714, 11027847, 11027868, 11028441, 11029201, 11029311, 11029703, 11029770, 11029916, 11029928, 11029936</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -15243,39 +15357,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01:46</t>
+          <t>23:38</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>11023181, 11023597, 11023831, 11026332, 11026371, 11026471, 11026982, 11027127, 11027960, 11028301, 11028727, 11028808, 11028934, 11029374, 11029387, 11029584, 11029924, 11030082</t>
+          <t>11026503, 11026751, 11026855, 11027003, 11027200, 11027767, 11029419, 11029552</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -15286,30 +15400,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>01:46</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>11020130, 11024000, 11026721, 11027000, 11027066, 11027703, 11027885, 11027947, 11028021, 11028080, 11028177, 11028556, 11028589, 11028703, 11028904, 11028960, 11029267, 11029701, 11029794, 11029825, 11029858, 11030155</t>
+          <t>11023181, 11023597, 11023831, 11026332, 11026371, 11026471, 11026982, 11027127, 11027960, 11028301, 11028727, 11028808, 11028934, 11029374, 11029387, 11029584, 11029924, 11030082</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -15324,30 +15438,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>11020116, 11021307, 11026207, 11026745, 11026956, 11027050, 11027430, 11027842, 11027893, 11027928, 11028296, 11028348, 11028565, 11028585, 11028806, 11028905, 11029116, 11029165, 11029177, 11029261</t>
+          <t>11007122, 11024000, 11026721, 11027066, 11027703, 11027885, 11028021, 11028080, 11028177, 11028556, 11028703, 11028904, 11028960, 11028981, 11029267, 11029290, 11029293, 11029701, 11029794, 11029825, 11029858, 11030155</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -15362,30 +15476,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11024415, 11026240, 11026554, 11026726, 11026950, 11027334, 11027462, 11027663, 11028206, 11028341, 11028344, 11028605, 11028747, 11029191, 11029219, 11029295, 11029403, 11029405, 11029528, 11029635, 11029719, 11029925</t>
+          <t>11020116, 11021307, 11026207, 11026555, 11026745, 11026956, 11027842, 11027893, 11027928, 11028296, 11028348, 11028565, 11028585, 11028806, 11028905, 11029116, 11029165, 11029177, 11029261, 11029935</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -15400,30 +15514,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>22:18</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>11028013</t>
+          <t>11024415, 11026240, 11026554, 11026726, 11026950, 11026992, 11027334, 11027462, 11027663, 11028206, 11028341, 11028344, 11028605, 11028747, 11029219, 11029295, 11029403, 11029528, 11029635, 11029719, 11029925, 11030289</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -15433,35 +15547,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>03:12</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>11024409, 11024762, 11026679, 11026867, 11026950, 11027201, 11027565, 11027767, 11027775, 11028186, 11028291, 11028891, 11028925, 11028946, 11029017, 11029146, 11029329, 11029402, 11029429, 11030039, 11030042, 11030078</t>
+          <t>11005920, 11020116, 11021307, 11026745, 11026956, 11027660, 11028013, 11028178, 11028408, 11028523, 11028689, 11028691, 11028865, 11028905, 11029393</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -15476,22 +15590,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>07:09</t>
+          <t>03:12</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -15499,7 +15613,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>11024876, 11026368, 11026533, 11026572, 11026848, 11027460, 11027562, 11027573, 11027601, 11027672, 11027940, 11028066, 11028220, 11028310, 11028694, 11029287, 11029304, 11029372, 11029724, 11029778, 11029830, 11030125</t>
+          <t>11024409, 11024762, 11026679, 11026867, 11026950, 11027201, 11027565, 11027767, 11027775, 11028186, 11028291, 11028891, 11028925, 11028946, 11029017, 11029146, 11029329, 11029402, 11029429, 11030039, 11030042, 11030078</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -15514,22 +15628,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -15537,7 +15651,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11024389, 11026449, 11026461, 11026634, 11026648, 11027067, 11027711, 11027847, 11027868, 11027939, 11027951, 11027969, 11028022, 11028332, 11028558, 11028567, 11028580, 11028690, 11029264, 11029365, 11029673, 11029943</t>
+          <t>11026461, 11026472, 11026541, 11026611, 11026901, 11027430, 11027835, 11027853, 11027857, 11027888, 11027915, 11028223, 11028411, 11028438, 11028442, 11028856, 11029774, 11029799, 11029927, 11029946, 11029974, 11029984</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -15552,30 +15666,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19:27</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11026801, 11026849, 11026902, 11027402, 11027435, 11027849, 11028855, 11028987, 11029017, 11029020, 11029137, 11029265, 11029476, 11029620, 11029731, 11029732, 11029804, 11029909, 11030039</t>
+          <t>11024389, 11026449, 11026461, 11026634, 11026648, 11027067, 11027847, 11027868, 11027939, 11027951, 11027969, 11028022, 11028332, 11028558, 11028567, 11028580, 11028690, 11028693, 11029264, 11029365, 11029673, 11029943</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -15590,30 +15704,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>11007757, 11026631, 11026648, 11026679, 11026802, 11026831, 11026903, 11026942, 11027368, 11027371, 11027399, 11027706, 11027714, 11027847, 11027868, 11028441, 11028971, 11029201, 11029703, 11029916, 11029928, 11029936</t>
+          <t>11026730, 11027056, 11027444, 11027533, 11028010, 11029773, 11029864, 11029887</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -15628,34 +15742,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Trip 6</t>
+          <t>Trip 5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>23:38</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>11026503, 11026751, 11026855, 11027003, 11027200, 11027767, 11029419, 11029552</t>
+          <t>11020130, 11026207, 11026251, 11026494, 11027715, 11027905, 11028589, 11028840, 11029277, 11029340, 11030055, 11030075</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -15714,20 +15828,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>11017088, 11026555, 11026750, 11027056, 11027068, 11027070, 11027444, 11027533, 11027916, 11027946, 11028099, 11028234, 11028531, 11028552, 11028574, 11028960, 11029196, 11029413, 11029773, 11029864, 11029941</t>
+          <t>11026631, 11026802, 11026901, 11027193, 11027368, 11027390, 11027533, 11027668, 11027717, 11027928, 11027943, 11028010, 11028338, 11028366, 11028660, 11028971, 11029474, 11029573, 11029774, 11029798, 11029799, 11029928</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -15765,7 +15879,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>11023597, 11026471, 11026503, 11026751, 11026982, 11027775, 11027869, 11028186, 11028291, 11028891, 11028934, 11029146, 11029170, 11029178, 11029329, 11029429, 11030078, 11030107</t>
+          <t>11023597, 11026471, 11026503, 11026751, 11026982, 11027775, 11027869, 11028186, 11028291, 11028891, 11028934, 11029017, 11029146, 11029329, 11029429, 11030039, 11030078, 11030107</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -15790,20 +15904,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>11024270, 11025099, 11026347, 11027323, 11027690, 11027948, 11028611, 11028849, 11029141, 11029147, 11029591, 11029638, 11029758, 11029770, 11029809, 11029877, 11030028, 11030154, 11030333</t>
+          <t>11007718, 11016423, 11019663, 11026707, 11026860, 11027565, 11028391, 11028809, 11028946, 11029195, 11029237, 11029252, 11029273, 11029334, 11029338, 11029402, 11029675, 11029878, 11029926, 11029938, 11029968, 11030211</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -15828,12 +15942,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -15841,7 +15955,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>11024106, 11026706, 11026869, 11026963, 11026992, 11026999, 11027303, 11027370, 11027403, 11028284, 11028557, 11028575, 11028738, 11028740, 11029464, 11029470, 11029498, 11029793, 11029818, 11029910, 11030001, 11030152</t>
+          <t>11023626, 11026323, 11026368, 11026533, 11026612, 11026673, 11026934, 11027072, 11027601, 11027711, 11027941, 11027946, 11027969, 11027977, 11028066, 11028220, 11028409, 11028709, 11029287, 11029319, 11029324, 11029372</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -15871,7 +15985,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>04:08</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -15879,7 +15993,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>11024415, 11026240, 11026726, 11027204, 11027334, 11027462, 11027877, 11028341, 11028344, 11028605, 11028747, 11029191, 11029219, 11029295, 11029403, 11029528, 11029766, 11029797, 11029925, 11029928, 11030084, 11030289</t>
+          <t>11026370, 11026673, 11026889, 11027050, 11027345, 11027566, 11027711, 11027901, 11027948, 11028218, 11028334, 11028348, 11028405, 11028558, 11028565, 11028599, 11028693, 11029161, 11029286, 11029456, 11029638, 11029877</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -15904,20 +16018,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>06:17</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>11027096, 11027176, 11027451, 11028950, 11029315, 11029912, 11030035</t>
+          <t>11019663, 11024106, 11026706, 11026707, 11026963, 11026999, 11027370, 11027403, 11028284, 11028557, 11028575, 11028740, 11028877, 11029273, 11029338, 11029464, 11029470, 11029793, 11029818, 11029910, 11029926, 11030152</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -15942,20 +16056,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>06:37</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>11001713, 11019006, 11021764, 11026407, 11026408, 11026429, 11026431, 11026468, 11026515, 11026615, 11027018, 11027565, 11028946, 11029334, 11029402, 11029498, 11029503, 11029655, 11029659, 11030211</t>
+          <t>11017088, 11026673, 11026750, 11027056, 11027068, 11027070, 11027444, 11027460, 11027916, 11028099, 11028234, 11028531, 11028552, 11028574, 11028960, 11029196, 11029205, 11029413, 11029773, 11029864, 11029941</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -15980,20 +16094,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>11020174, 11026396, 11026847, 11026907, 11027058, 11027329, 11027858, 11027971, 11028023, 11028134, 11028467, 11029106, 11029268, 11029394, 11029688, 11029700, 11029784, 11029801, 11029917, 11029948, 11030195</t>
+          <t>11001713, 11019006, 11021764, 11026407, 11026408, 11026429, 11026431, 11026468, 11026515, 11026615, 11027018, 11027565, 11028946, 11029334, 11029402, 11029498, 11029503, 11029655, 11029659, 11030211</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -16003,35 +16117,35 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>06:23</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>11024033, 11024562, 11026323, 11026756, 11026847, 11026907, 11027101, 11027846, 11027889, 11028017, 11028020, 11028178, 11028334, 11028402, 11028408, 11028981, 11029236, 11029272, 11029951, 11029977, 11030118, 11030182</t>
+          <t>11020174, 11026396, 11026847, 11026907, 11027058, 11027329, 11027858, 11027971, 11028023, 11028134, 11028467, 11029106, 11029268, 11029394, 11029688, 11029700, 11029784, 11029801, 11029917, 11029948, 11030195</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -16046,30 +16160,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>11021111, 11024033, 11024562, 11026454, 11026611, 11026730, 11026756, 11027101, 11027292, 11027327, 11027367, 11027846, 11027889, 11028017, 11028020, 11028339, 11028402, 11029113, 11029205, 11029236, 11029272, 11029304, 11029935, 11029948, 11029951, 11029977, 11030118, 11030175, 11030182</t>
+          <t>11024415, 11026240, 11026726, 11027204, 11027334, 11027462, 11028341, 11028344, 11028605, 11028747, 11029108, 11029191, 11029219, 11029295, 11029403, 11029405, 11029528, 11029719, 11029797, 11029925, 11030084</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -16084,30 +16198,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>21:46</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>11023626, 11026323, 11026368, 11026533, 11026612, 11026673, 11026934, 11027072, 11027601, 11027941, 11027946, 11027969, 11027977, 11028066, 11028220, 11028409, 11028694, 11028709, 11029287, 11029319, 11029324, 11029372</t>
+          <t>11021111, 11024033, 11024562, 11024876, 11026454, 11026756, 11027050, 11027101, 11027292, 11027327, 11027430, 11027846, 11027889, 11028017, 11028020, 11028310, 11028339, 11028402, 11028856, 11029236, 11029272, 11029325, 11029927, 11029948, 11029951, 11029977, 11030118, 11030175, 11030182</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -16117,35 +16231,35 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>03:47</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>11026555, 11026673, 11027298, 11027345, 11027711, 11028218, 11028348, 11028405, 11028558, 11028565, 11028599, 11028693, 11029161, 11029286, 11029290, 11029456</t>
+          <t>11024106, 11026706, 11026869, 11026963, 11026999, 11027303, 11027370, 11027403, 11028284, 11028557, 11028575, 11028738, 11028740, 11029058, 11029464, 11029470, 11029498, 11029793, 11029818, 11029910, 11030001, 11030152</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -16160,30 +16274,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>04:08</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>11026631, 11026802, 11026901, 11027193, 11027368, 11027390, 11027533, 11027668, 11027717, 11027928, 11027943, 11028010, 11028338, 11028366, 11028660, 11028971, 11029474, 11029573, 11029774, 11029798, 11029799, 11029928</t>
+          <t>11024270, 11026347, 11026554, 11026903, 11027371, 11027400, 11027663, 11027760, 11027877, 11028206, 11028441, 11028937, 11029164, 11029170, 11029178, 11029483, 11029635, 11029766, 11029928, 11030183, 11030289</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -16198,30 +16312,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>05:54</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11001526, 11023181, 11024024, 11024409, 11024762, 11026462, 11026632, 11027127, 11027191, 11028959, 11029419, 11029552, 11030042</t>
+          <t>11025826, 11026492, 11026633, 11026802, 11027343, 11027368, 11027714, 11027869, 11028222, 11028555, 11029070, 11029222, 11029311, 11029371, 11029703, 11029814, 11029856, 11029916, 11029920, 11029923, 11029936</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -16236,22 +16350,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -16259,7 +16373,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>11007122, 11020130, 11026889, 11027066, 11027077, 11027324, 11027350, 11027566, 11027865, 11027901, 11027932, 11028021, 11028333, 11028395, 11028556, 11028563, 11028873, 11029223, 11029267, 11029585, 11029701, 11029724</t>
+          <t>11007718, 11016423, 11026860, 11026869, 11026992, 11027418, 11028214, 11028391, 11028809, 11028911, 11029058, 11029195, 11029237, 11029252, 11029597, 11029675, 11029707, 11029720, 11029878, 11029938, 11029968, 11030001</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -16274,68 +16388,68 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>21:23</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>11025826, 11026492, 11026633, 11026689, 11027096, 11027343, 11027927, 11027938, 11028016, 11028222, 11028555, 11029070, 11029483, 11029597, 11029707, 11029814, 11029920, 11029923</t>
+          <t>11004911, 11026348, 11026568, 11026642, 11026812, 11026943, 11027375, 11027706, 11027714, 11027849, 11028244, 11028302, 11029117, 11029156, 11029191, 11029201, 11029763, 11029903, 11030091, 11030093</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 5</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>04:19</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>11024270, 11026347, 11026370, 11026554, 11026903, 11027371, 11027400, 11027663, 11027760, 11027948, 11028206, 11028441, 11028937, 11029108, 11029164, 11029170, 11029178, 11029483, 11029635, 11029638, 11029877, 11030183</t>
+          <t>11001526, 11023181, 11024024, 11024409, 11024762, 11026462, 11026632, 11027127, 11027191, 11028959, 11029419, 11029552, 11030042</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -16345,35 +16459,35 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 6</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>11026027, 11026689, 11026802, 11027251, 11027302, 11027368, 11027668, 11027714, 11027717, 11027869, 11027927, 11027938, 11027943, 11028016, 11028338, 11028806, 11029311, 11029798</t>
+          <t>11007975, 11025099, 11026237, 11026244, 11026281, 11026347, 11026478, 11026814, 11026932, 11026945, 11027301, 11027302, 11027365, 11027390, 11027717, 11028338, 11028588, 11028859, 11029168, 11029428, 11029573, 11029811</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -16388,30 +16502,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>03:58</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>11007718, 11016423, 11026860, 11026869, 11026992, 11027418, 11028214, 11028391, 11028809, 11028911, 11029058, 11029195, 11029237, 11029252, 11029597, 11029675, 11029707, 11029720, 11029878, 11029938, 11029968, 11030001</t>
+          <t>11024745, 11026942, 11027062, 11027390, 11027399, 11027613, 11027685, 11027690, 11027837, 11027875, 11028568, 11028571, 11028611, 11028707, 11028746, 11028849, 11028971, 11029148, 11029177, 11029969</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -16426,30 +16540,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>11026890, 11027582, 11027835, 11027853, 11027857, 11027957, 11028163, 11028433, 11028438, 11029325</t>
+          <t>11026027, 11026631, 11026689, 11027251, 11027302, 11027668, 11027706, 11027717, 11027927, 11027938, 11027943, 11028016, 11028338, 11028806, 11029201, 11029770, 11029798</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -16464,30 +16578,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>11004911, 11026348, 11026568, 11026642, 11026812, 11026943, 11027375, 11027706, 11027714, 11027849, 11028244, 11028302, 11029117, 11029156, 11029201, 11029454, 11029763, 11029903, 11030091, 11030093</t>
+          <t>11007757, 11021548, 11022368, 11024116, 11024117, 11026637, 11027396, 11027432, 11027891, 11028587, 11028673, 11028866, 11028867, 11029312, 11029333, 11029527, 11029758, 11029879, 11030028, 11030136, 11030154, 11030224</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -16502,12 +16616,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Trip 6</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -16550,20 +16664,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>03:15</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>06:27</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>11020174, 11027058, 11027090, 11027292, 11027327, 11027329, 11027858, 11027971, 11027977, 11028023, 11028339, 11028467, 11029106, 11029268, 11029394, 11029688, 11029700, 11029784, 11029801, 11029917, 11029948</t>
+          <t>11024033, 11024562, 11026454, 11026756, 11026847, 11026907, 11027101, 11027846, 11027889, 11028017, 11028020, 11028178, 11028402, 11028408, 11029236, 11029272, 11029951, 11029977, 11030118, 11030182</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -16588,20 +16702,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>11001526, 11021111, 11026251, 11026494, 11026572, 11026632, 11026673, 11026890, 11026934, 11027298, 11027345, 11027582, 11027902, 11027905, 11028310, 11028612, 11028692, 11028959, 11029266, 11029277, 11030075</t>
+          <t>11026611, 11026890, 11027582, 11027835, 11027853, 11027857, 11027957, 11028163, 11028433, 11028438</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -16626,20 +16740,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>11026942, 11027062, 11027193, 11027251, 11027400, 11027685, 11027837, 11027875, 11027888, 11027915, 11028223, 11028286, 11028568, 11028571, 11028707, 11029108, 11029148, 11029164, 11029299, 11029353, 11029557, 11029766, 11029969, 11030289</t>
+          <t>11001526, 11021111, 11026251, 11026494, 11026632, 11026890, 11026934, 11027345, 11027582, 11027711, 11027902, 11027905, 11028612, 11028692, 11028959, 11029113, 11029266, 11029277, 11029946, 11030013, 11030075</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -16664,20 +16778,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>11004911, 11020175, 11021740, 11026568, 11026822, 11027375, 11028244, 11028286, 11028302, 11028991, 11029117, 11029170, 11029498, 11029561, 11029757, 11029903, 11030093</t>
+          <t>11024270, 11026308, 11027062, 11027193, 11027251, 11027400, 11027685, 11027837, 11027875, 11027888, 11027915, 11028223, 11028568, 11028571, 11029108, 11029141, 11029147, 11029164, 11029170, 11029178, 11029405, 11029591, 11029766, 11029934</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -16702,20 +16816,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>01:58</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>11005920, 11020116, 11021307, 11026745, 11026956, 11027660, 11028013, 11028178, 11028408, 11028523, 11028689, 11028691, 11028865, 11028905, 11029393</t>
+          <t>11004911, 11020175, 11021740, 11026568, 11026679, 11026822, 11027375, 11027690, 11028244, 11028286, 11028302, 11028971, 11028991, 11029117, 11029170, 11029498, 11029561, 11029757, 11029809, 11029903, 11030093</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -16725,35 +16839,35 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 6</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>04:46</t>
+          <t>01:44</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>11024745, 11026942, 11027062, 11027390, 11027399, 11027613, 11027685, 11027690, 11027837, 11027875, 11028568, 11028571, 11028611, 11028707, 11028746, 11028849, 11028971, 11029148, 11029177, 11029405, 11029719, 11029969</t>
+          <t>11028474, 11029454</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -16768,30 +16882,30 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>05:15</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>06:09</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>11025826, 11026492, 11026631, 11026633, 11027343, 11027706, 11028222, 11028555, 11029070, 11029201, 11029222, 11029371, 11029703, 11029770, 11029814, 11029856, 11029916, 11029920, 11029923, 11029936</t>
+          <t>11020174, 11027058, 11027090, 11027292, 11027327, 11027329, 11027858, 11027971, 11027977, 11028023, 11028339, 11028467, 11029106, 11029268, 11029394, 11029688, 11029700, 11029784, 11029801, 11029917, 11029948</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -16806,30 +16920,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>11024296, 11025033, 11026319, 11026453, 11026766, 11026884, 11027060, 11027366, 11027525, 11027712, 11027713, 11027856, 11027865, 11028014, 11028217, 11028395, 11028553, 11029262, 11029276, 11029585, 11029863, 11030012</t>
+          <t>11007757, 11023181, 11026822, 11026831, 11026890, 11027127, 11027565, 11027582, 11027877, 11027891, 11027968, 11028441, 11028926, 11028946, 11028991, 11029334, 11029402, 11029561, 11029757, 11029809, 11030042, 11030211, 11030334</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -16844,12 +16958,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -16859,15 +16973,15 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>11007975, 11026237, 11026244, 11026281, 11026308, 11026478, 11026814, 11026932, 11026945, 11027301, 11027302, 11027365, 11027390, 11027717, 11028214, 11028338, 11028588, 11028859, 11029168, 11029428, 11029573, 11029811</t>
+          <t>11017088, 11027000, 11027068, 11027070, 11027904, 11027932, 11027947, 11028099, 11028234, 11028366, 11028531, 11028552, 11028574, 11028660, 11028873, 11029266, 11029340, 11029413, 11029474, 11030013</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -16882,30 +16996,30 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>11022368, 11023181, 11024116, 11024117, 11024409, 11024762, 11027127, 11027396, 11027432, 11027767, 11027895, 11028587, 11028673, 11028867, 11029333, 11029419, 11029527, 11029552, 11029879, 11030042, 11030224</t>
+          <t>11026348, 11026642, 11026812, 11026943, 11027877, 11027893, 11027968, 11028296, 11028926, 11029116, 11029156, 11029165, 11029177, 11029763, 11029765, 11029970, 11030091, 11030334</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -16973,7 +17087,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>06:04</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -16981,7 +17095,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>11007757, 11021548, 11022368, 11024116, 11024117, 11026637, 11027396, 11027432, 11027891, 11028587, 11028673, 11028866, 11028867, 11029312, 11029333, 11029527, 11029758, 11029879, 11030028, 11030136, 11030154, 11030224</t>
+          <t>11015073, 11023626, 11026612, 11026750, 11027072, 11027077, 11027324, 11027350, 11027573, 11027865, 11027916, 11027941, 11028333, 11028395, 11028409, 11028563, 11028692, 11028709, 11029223, 11029324, 11029585, 11029941</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -17006,20 +17120,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>11007122, 11015073, 11022532, 11023626, 11026541, 11026612, 11026750, 11026889, 11027072, 11027077, 11027090, 11027324, 11027350, 11027566, 11027901, 11027941, 11028409, 11028411, 11028563, 11028709, 11029223, 11029324</t>
+          <t>11026867, 11027201, 11027955, 11028301, 11028474, 11028727, 11028808, 11029584, 11029912, 11029924, 11030063, 11030082</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -17044,24 +17158,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>11007757, 11023181, 11026822, 11026831, 11026890, 11027127, 11027565, 11027582, 11027877, 11027891, 11027968, 11028441, 11028926, 11028946, 11028991, 11029334, 11029402, 11029561, 11029757, 11029809, 11030042, 11030211, 11030334</t>
+          <t>11027298, 11027562, 11027940, 11028218, 11028599, 11028694, 11028953, 11029161, 11029286, 11029290, 11029456</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -17082,20 +17196,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>11017088, 11027068, 11027070, 11027916, 11027932, 11028099, 11028234, 11028333, 11028366, 11028531, 11028552, 11028574, 11028660, 11028692, 11028873, 11029340, 11029413, 11029474, 11029941, 11030013</t>
+          <t>11007122, 11020130, 11026889, 11027066, 11027077, 11027324, 11027350, 11027566, 11027865, 11027901, 11027932, 11028021, 11028333, 11028395, 11028556, 11028563, 11028873, 11029223, 11029267, 11029585, 11029701, 11029724</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -17125,7 +17239,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -17133,11 +17247,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>11026348, 11026642, 11026812, 11026943, 11027877, 11027893, 11027968, 11028296, 11028926, 11029116, 11029156, 11029165, 11029177, 11029763, 11029765, 11029970, 11030091, 11030334</t>
+          <t>11025826, 11026492, 11026633, 11026689, 11027096, 11027343, 11027927, 11027938, 11028016, 11028222, 11028555, 11029070, 11029483, 11029597, 11029707, 11029814, 11029920, 11029923</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -17158,12 +17272,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>05:03</t>
+          <t>04:48</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -17171,7 +17285,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>11026449, 11026890, 11027582, 11027842, 11027847, 11027868, 11028533, 11028585, 11029264, 11029289, 11029325, 11029365, 11029943, 11029976</t>
+          <t>11026449, 11026890, 11027582, 11027842, 11027847, 11027868, 11028310, 11028585, 11029264, 11029289, 11029325, 11029365, 11029943, 11029976</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -17196,12 +17310,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>06:24</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -17209,7 +17323,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>11015482, 11026461, 11026472, 11026870, 11026901, 11027050, 11027430, 11027835, 11027853, 11027857, 11027888, 11027915, 11028223, 11028438, 11028442, 11028856, 11029293, 11029774, 11029799, 11029927, 11029974, 11029979</t>
+          <t>11022532, 11026323, 11026368, 11026533, 11026572, 11026848, 11027090, 11027562, 11027601, 11027672, 11027940, 11028066, 11028220, 11028694, 11029113, 11029287, 11029304, 11029372, 11029724, 11029778, 11029830, 11030125</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -17234,20 +17348,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>11026867, 11027201, 11027955, 11028301, 11028474, 11028727, 11028808, 11029584, 11029912, 11029924, 11030063, 11030082</t>
+          <t>11026281, 11026801, 11026902, 11027096, 11027402, 11028855, 11028987, 11029020, 11029265, 11029315, 11029371, 11029476, 11029620, 11029804, 11029909, 11029970, 11030333</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -17272,12 +17386,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -17285,7 +17399,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>11026207, 11027056, 11027444, 11028010, 11029773, 11029864, 11029887, 11029984</t>
+          <t>11027176, 11027451, 11028950, 11029299, 11029353, 11029557, 11029912, 11030035</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -17310,20 +17424,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>11026251, 11026454, 11026494, 11027000, 11027715, 11027904, 11027905, 11028840, 11029266, 11029277, 11030055, 11030075</t>
+          <t>11026671, 11026849, 11026942, 11027345, 11027435, 11027567, 11027948, 11027957, 11028163, 11028214, 11028286, 11028433, 11028442, 11028611, 11028707, 11028849, 11029148, 11029261, 11029638, 11029732, 11029758, 11029877, 11029969, 11029974, 11030028, 11030154, 11030288, 11030333</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -17333,39 +17447,39 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Trip 1</t>
+          <t>Trip 6</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>06:17</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>11019663, 11024106, 11026706, 11026707, 11026963, 11026999, 11027370, 11027403, 11028284, 11028557, 11028575, 11028740, 11028877, 11029273, 11029338, 11029464, 11029470, 11029793, 11029818, 11029910, 11029926, 11030152</t>
+          <t>11015482, 11022532, 11026572, 11028411, 11029293, 11029304, 11029349, 11029778, 11029979, 11030125</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -17376,30 +17490,30 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Trip 2</t>
+          <t>Trip 1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>11007975, 11020175, 11021740, 11026237, 11026244, 11026478, 11026615, 11026814, 11026932, 11026945, 11027301, 11027365, 11027371, 11028588, 11028859, 11028877, 11029168, 11029428, 11029498, 11029765, 11029811</t>
+          <t>11015482, 11024296, 11025033, 11026319, 11026453, 11026766, 11026870, 11026884, 11027060, 11027366, 11027525, 11027712, 11027713, 11027856, 11028014, 11028217, 11028553, 11029262, 11029276, 11029863, 11029979, 11030012</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -17414,12 +17528,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Trip 3</t>
+          <t>Trip 2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -17452,30 +17566,30 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Trip 4</t>
+          <t>Trip 3</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>11026555, 11026671, 11027345, 11027562, 11027567, 11027902, 11027940, 11027957, 11028163, 11028218, 11028433, 11028442, 11028599, 11028693, 11028746, 11028856, 11028953, 11029161, 11029261, 11029286, 11029290, 11029293, 11029311, 11029456, 11029927, 11029974, 11030144, 11030288, 11030333</t>
+          <t>11026801, 11026902, 11027323, 11027402, 11027849, 11028746, 11028855, 11028987, 11029017, 11029020, 11029137, 11029265, 11029476, 11029620, 11029731, 11029804, 11029909, 11030039, 11030144</t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -17490,71 +17604,33 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Trip 5</t>
+          <t>Trip 4</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>11015482, 11022532, 11028411, 11029349, 11029778, 11029979, 11030125</t>
+          <t>11022368, 11023181, 11024116, 11024117, 11024409, 11024762, 11027127, 11027396, 11027432, 11027767, 11027895, 11028587, 11028673, 11028867, 11029333, 11029419, 11029527, 11029552, 11029879, 11030042, 11030224</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>D13</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Trip 6</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>T6</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>01:38</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>11028474</t>
-        </is>
-      </c>
-      <c r="H68" t="n">
         <v>0</v>
       </c>
     </row>
